--- a/exports/eaglevents-hour-logs.xlsx
+++ b/exports/eaglevents-hour-logs.xlsx
@@ -14,9 +14,8 @@
     <sheet name="Kayley Jaskolski" sheetId="9" r:id="rId9"/>
     <sheet name="Keagan Schinner" sheetId="10" r:id="rId10"/>
     <sheet name="Merl Stroman" sheetId="11" r:id="rId11"/>
-    <sheet name="Miller Mayert" sheetId="12" r:id="rId12"/>
-    <sheet name="Morgan Johnson" sheetId="13" r:id="rId13"/>
-    <sheet name="Nicholas Villiers" sheetId="14" r:id="rId14"/>
+    <sheet name="Morgan Johnson" sheetId="12" r:id="rId12"/>
+    <sheet name="Nicholas Villiers" sheetId="13" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
@@ -410,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T446"/>
+  <dimension ref="A1:T420"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -22486,40 +22485,40 @@
     </row>
     <row r="357">
       <c r="A357">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B357" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C357" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D357" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E357" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F357" t="str">
-        <v>Granular Midst Perky Everlasting</v>
+        <v>Visionary Supportive Carefree Unto</v>
       </c>
       <c r="G357" t="str">
-        <v>7587773</v>
+        <v>6504796</v>
       </c>
       <c r="H357" t="str">
-        <v/>
+        <v>ZD075695</v>
       </c>
       <c r="I357" t="str">
-        <v>2019-02-10T16:38:01.088Z</v>
+        <v>2019-02-16T11:08:22.059Z</v>
       </c>
       <c r="J357" t="str">
-        <v>2/10/2019, 11:38:01 AM</v>
+        <v>2/16/2019, 6:08:22 AM</v>
       </c>
       <c r="K357" t="str">
-        <v>2019-02-10T19:38:01.088Z</v>
+        <v>2019-02-16T12:08:22.059Z</v>
       </c>
       <c r="L357" t="str">
-        <v>2/10/2019, 2:38:01 PM</v>
+        <v>2/16/2019, 7:08:22 AM</v>
       </c>
       <c r="M357" t="str">
         <v>Calendar</v>
@@ -22531,57 +22530,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P357" t="str">
-        <v>2019-02-10T16:38:01.088Z</v>
+        <v>2019-02-16T11:08:22.059Z</v>
       </c>
       <c r="Q357" t="str">
-        <v>2/10/2019, 11:38:01 AM</v>
+        <v>2/16/2019, 6:08:22 AM</v>
       </c>
       <c r="R357" t="str">
-        <v>2019-02-10T19:11:01.088Z</v>
+        <v>2019-02-16T12:05:22.059Z</v>
       </c>
       <c r="S357" t="str">
-        <v>2/10/2019, 2:11:01 PM</v>
+        <v>2/16/2019, 7:05:22 AM</v>
       </c>
       <c r="T357">
-        <v>153</v>
+        <v>57</v>
       </c>
     </row>
     <row r="358">
       <c r="A358">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B358" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C358" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D358" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E358" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F358" t="str">
-        <v>Synergistic Quit Trek But</v>
+        <v>Cutting-Edge Approximate Instead Front</v>
       </c>
       <c r="G358" t="str">
-        <v>1448827</v>
+        <v>2742534</v>
       </c>
       <c r="H358" t="str">
         <v/>
       </c>
       <c r="I358" t="str">
-        <v>2019-09-26T07:04:01.022Z</v>
+        <v>2019-03-27T05:02:23.316Z</v>
       </c>
       <c r="J358" t="str">
-        <v>9/26/2019, 3:04:01 AM</v>
+        <v>3/27/2019, 1:02:23 AM</v>
       </c>
       <c r="K358" t="str">
-        <v>2019-09-26T09:04:01.022Z</v>
+        <v>2019-03-27T08:02:23.316Z</v>
       </c>
       <c r="L358" t="str">
-        <v>9/26/2019, 5:04:01 AM</v>
+        <v>3/27/2019, 4:02:23 AM</v>
       </c>
       <c r="M358" t="str">
         <v>Calendar</v>
@@ -22593,57 +22592,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P358" t="str">
-        <v>2019-09-26T07:04:01.022Z</v>
+        <v>2019-03-27T05:02:23.316Z</v>
       </c>
       <c r="Q358" t="str">
-        <v>9/26/2019, 3:04:01 AM</v>
+        <v>3/27/2019, 1:02:23 AM</v>
       </c>
       <c r="R358" t="str">
-        <v>2019-09-26T08:03:01.022Z</v>
+        <v>2019-03-27T07:47:23.316Z</v>
       </c>
       <c r="S358" t="str">
-        <v>9/26/2019, 4:03:01 AM</v>
+        <v>3/27/2019, 3:47:23 AM</v>
       </c>
       <c r="T358">
-        <v>59</v>
+        <v>165</v>
       </c>
     </row>
     <row r="359">
       <c r="A359">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="B359" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C359" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D359" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E359" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F359" t="str">
-        <v>Impactful Unimpressively</v>
+        <v>Granular Furthermore</v>
       </c>
       <c r="G359" t="str">
-        <v>8687107</v>
+        <v>3402553</v>
       </c>
       <c r="H359" t="str">
-        <v>ZD155686</v>
+        <v/>
       </c>
       <c r="I359" t="str">
-        <v>2019-11-23T22:56:47.005Z</v>
+        <v>2019-05-11T22:23:52.836Z</v>
       </c>
       <c r="J359" t="str">
-        <v>11/23/2019, 5:56:47 PM</v>
+        <v>5/11/2019, 6:23:52 PM</v>
       </c>
       <c r="K359" t="str">
-        <v>2019-11-24T02:56:47.005Z</v>
+        <v>2019-05-12T01:23:52.836Z</v>
       </c>
       <c r="L359" t="str">
-        <v>11/23/2019, 9:56:47 PM</v>
+        <v>5/11/2019, 9:23:52 PM</v>
       </c>
       <c r="M359" t="str">
         <v>Calendar</v>
@@ -22655,57 +22654,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P359" t="str">
-        <v>2019-11-23T22:56:47.005Z</v>
+        <v>2019-05-11T22:23:52.836Z</v>
       </c>
       <c r="Q359" t="str">
-        <v>11/23/2019, 5:56:47 PM</v>
+        <v>5/11/2019, 6:23:52 PM</v>
       </c>
       <c r="R359" t="str">
-        <v>2019-11-24T01:11:47.005Z</v>
+        <v>2019-05-11T23:01:52.836Z</v>
       </c>
       <c r="S359" t="str">
-        <v>11/23/2019, 8:11:47 PM</v>
+        <v>5/11/2019, 7:01:52 PM</v>
       </c>
       <c r="T359">
-        <v>135</v>
+        <v>38</v>
       </c>
     </row>
     <row r="360">
       <c r="A360">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B360" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C360" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D360" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E360" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F360" t="str">
-        <v>Plug-And-Play Nun</v>
+        <v>Proactive Suitcase As Before</v>
       </c>
       <c r="G360" t="str">
-        <v>8055884</v>
+        <v>7065660</v>
       </c>
       <c r="H360" t="str">
-        <v>ZD061746</v>
+        <v>ZD399054</v>
       </c>
       <c r="I360" t="str">
-        <v>2020-01-08T18:32:37.824Z</v>
+        <v>2019-12-17T00:23:11.207Z</v>
       </c>
       <c r="J360" t="str">
-        <v>1/8/2020, 1:32:37 PM</v>
+        <v>12/16/2019, 7:23:11 PM</v>
       </c>
       <c r="K360" t="str">
-        <v>2020-01-08T20:32:37.824Z</v>
+        <v>2019-12-17T03:23:11.207Z</v>
       </c>
       <c r="L360" t="str">
-        <v>1/8/2020, 3:32:37 PM</v>
+        <v>12/16/2019, 10:23:11 PM</v>
       </c>
       <c r="M360" t="str">
         <v>Calendar</v>
@@ -22717,57 +22716,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P360" t="str">
-        <v>2020-01-08T18:32:37.824Z</v>
+        <v>2019-12-17T00:23:11.207Z</v>
       </c>
       <c r="Q360" t="str">
-        <v>1/8/2020, 1:32:37 PM</v>
+        <v>12/16/2019, 7:23:11 PM</v>
       </c>
       <c r="R360" t="str">
-        <v>2020-01-08T19:39:37.824Z</v>
+        <v>2019-12-17T02:13:11.207Z</v>
       </c>
       <c r="S360" t="str">
-        <v>1/8/2020, 2:39:37 PM</v>
+        <v>12/16/2019, 9:13:11 PM</v>
       </c>
       <c r="T360">
-        <v>67</v>
+        <v>110</v>
       </c>
     </row>
     <row r="361">
       <c r="A361">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B361" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C361" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D361" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E361" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F361" t="str">
-        <v>Plug-And-Play Yum Versus Yowza</v>
+        <v>Proactive Euphonium Blindly As</v>
       </c>
       <c r="G361" t="str">
-        <v>1183382</v>
+        <v>1105604</v>
       </c>
       <c r="H361" t="str">
-        <v>ZD455800</v>
+        <v/>
       </c>
       <c r="I361" t="str">
-        <v>2020-09-04T01:37:54.128Z</v>
+        <v>2020-04-20T13:22:35.416Z</v>
       </c>
       <c r="J361" t="str">
-        <v>9/3/2020, 9:37:54 PM</v>
+        <v>4/20/2020, 9:22:35 AM</v>
       </c>
       <c r="K361" t="str">
-        <v>2020-09-04T03:37:54.128Z</v>
+        <v>2020-04-20T15:22:35.416Z</v>
       </c>
       <c r="L361" t="str">
-        <v>9/3/2020, 11:37:54 PM</v>
+        <v>4/20/2020, 11:22:35 AM</v>
       </c>
       <c r="M361" t="str">
         <v>Calendar</v>
@@ -22779,57 +22778,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P361" t="str">
-        <v>2020-09-04T01:37:54.128Z</v>
+        <v>2020-04-20T13:22:35.416Z</v>
       </c>
       <c r="Q361" t="str">
-        <v>9/3/2020, 9:37:54 PM</v>
+        <v>4/20/2020, 9:22:35 AM</v>
       </c>
       <c r="R361" t="str">
-        <v>2020-09-04T03:32:54.128Z</v>
+        <v>2020-04-20T14:15:35.416Z</v>
       </c>
       <c r="S361" t="str">
-        <v>9/3/2020, 11:32:54 PM</v>
+        <v>4/20/2020, 10:15:35 AM</v>
       </c>
       <c r="T361">
-        <v>115</v>
+        <v>53</v>
       </c>
     </row>
     <row r="362">
       <c r="A362">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="B362" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C362" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D362" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E362" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F362" t="str">
-        <v>Value-Added Upon</v>
+        <v>AI-Driven Cantaloupe And Dissemble</v>
       </c>
       <c r="G362" t="str">
-        <v>6110501</v>
+        <v>6870326</v>
       </c>
       <c r="H362" t="str">
         <v/>
       </c>
       <c r="I362" t="str">
-        <v>2020-09-09T18:53:33.138Z</v>
+        <v>2020-05-25T17:54:31.159Z</v>
       </c>
       <c r="J362" t="str">
-        <v>9/9/2020, 2:53:33 PM</v>
+        <v>5/25/2020, 1:54:31 PM</v>
       </c>
       <c r="K362" t="str">
-        <v>2020-09-09T19:53:33.138Z</v>
+        <v>2020-05-25T20:54:31.159Z</v>
       </c>
       <c r="L362" t="str">
-        <v>9/9/2020, 3:53:33 PM</v>
+        <v>5/25/2020, 4:54:31 PM</v>
       </c>
       <c r="M362" t="str">
         <v>Calendar</v>
@@ -22841,57 +22840,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P362" t="str">
-        <v>2020-09-09T18:53:33.138Z</v>
+        <v>2020-05-25T17:54:31.159Z</v>
       </c>
       <c r="Q362" t="str">
-        <v>9/9/2020, 2:53:33 PM</v>
+        <v>5/25/2020, 1:54:31 PM</v>
       </c>
       <c r="R362" t="str">
-        <v>2020-09-09T19:51:33.138Z</v>
+        <v>2020-05-25T18:26:31.159Z</v>
       </c>
       <c r="S362" t="str">
-        <v>9/9/2020, 3:51:33 PM</v>
+        <v>5/25/2020, 2:26:31 PM</v>
       </c>
       <c r="T362">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="363">
       <c r="A363">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="B363" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C363" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D363" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E363" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F363" t="str">
-        <v>Cutting-Edge Amid Which Uh-Huh</v>
+        <v>End-To-End Irk</v>
       </c>
       <c r="G363" t="str">
-        <v>9499602</v>
+        <v>8196665</v>
       </c>
       <c r="H363" t="str">
-        <v>ZD830328</v>
+        <v/>
       </c>
       <c r="I363" t="str">
-        <v>2021-01-14T17:28:48.397Z</v>
+        <v>2020-07-29T09:50:52.438Z</v>
       </c>
       <c r="J363" t="str">
-        <v>1/14/2021, 12:28:48 PM</v>
+        <v>7/29/2020, 5:50:52 AM</v>
       </c>
       <c r="K363" t="str">
-        <v>2021-01-14T19:28:48.397Z</v>
+        <v>2020-07-29T10:50:52.438Z</v>
       </c>
       <c r="L363" t="str">
-        <v>1/14/2021, 2:28:48 PM</v>
+        <v>7/29/2020, 6:50:52 AM</v>
       </c>
       <c r="M363" t="str">
         <v>Calendar</v>
@@ -22903,57 +22902,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P363" t="str">
-        <v>2021-01-14T17:28:48.397Z</v>
+        <v>2020-07-29T09:50:52.438Z</v>
       </c>
       <c r="Q363" t="str">
-        <v>1/14/2021, 12:28:48 PM</v>
+        <v>7/29/2020, 5:50:52 AM</v>
       </c>
       <c r="R363" t="str">
-        <v>2021-01-14T18:34:48.397Z</v>
+        <v>2020-07-29T10:37:52.438Z</v>
       </c>
       <c r="S363" t="str">
-        <v>1/14/2021, 1:34:48 PM</v>
+        <v>7/29/2020, 6:37:52 AM</v>
       </c>
       <c r="T363">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="364">
       <c r="A364">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="B364" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C364" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D364" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E364" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F364" t="str">
-        <v>Strategic Loosely Along Spherical</v>
+        <v>Dynamic Cautious</v>
       </c>
       <c r="G364" t="str">
-        <v>3192905</v>
+        <v>3434194</v>
       </c>
       <c r="H364" t="str">
-        <v>ZD041990</v>
+        <v/>
       </c>
       <c r="I364" t="str">
-        <v>2021-01-27T00:36:18.569Z</v>
+        <v>2020-09-10T14:37:44.794Z</v>
       </c>
       <c r="J364" t="str">
-        <v>1/26/2021, 7:36:18 PM</v>
+        <v>9/10/2020, 10:37:44 AM</v>
       </c>
       <c r="K364" t="str">
-        <v>2021-01-27T04:36:18.569Z</v>
+        <v>2020-09-10T17:37:44.794Z</v>
       </c>
       <c r="L364" t="str">
-        <v>1/26/2021, 11:36:18 PM</v>
+        <v>9/10/2020, 1:37:44 PM</v>
       </c>
       <c r="M364" t="str">
         <v>Calendar</v>
@@ -22965,57 +22964,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P364" t="str">
-        <v>2021-01-27T00:36:18.569Z</v>
+        <v>2020-09-10T14:37:44.794Z</v>
       </c>
       <c r="Q364" t="str">
-        <v>1/26/2021, 7:36:18 PM</v>
+        <v>9/10/2020, 10:37:44 AM</v>
       </c>
       <c r="R364" t="str">
-        <v>2021-01-27T04:34:18.569Z</v>
+        <v>2020-09-10T17:19:44.794Z</v>
       </c>
       <c r="S364" t="str">
-        <v>1/26/2021, 11:34:18 PM</v>
+        <v>9/10/2020, 1:19:44 PM</v>
       </c>
       <c r="T364">
-        <v>238</v>
+        <v>162</v>
       </c>
     </row>
     <row r="365">
       <c r="A365">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B365" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C365" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D365" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E365" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F365" t="str">
-        <v>Real-Time Ew</v>
+        <v>Killer Till Monthly Ick</v>
       </c>
       <c r="G365" t="str">
-        <v>2846707</v>
+        <v>7069792</v>
       </c>
       <c r="H365" t="str">
-        <v>ZD166749</v>
+        <v/>
       </c>
       <c r="I365" t="str">
-        <v>2021-06-20T00:42:53.876Z</v>
+        <v>2021-07-18T09:48:25.476Z</v>
       </c>
       <c r="J365" t="str">
-        <v>6/19/2021, 8:42:53 PM</v>
+        <v>7/18/2021, 5:48:25 AM</v>
       </c>
       <c r="K365" t="str">
-        <v>2021-06-20T03:42:53.876Z</v>
+        <v>2021-07-18T12:48:25.476Z</v>
       </c>
       <c r="L365" t="str">
-        <v>6/19/2021, 11:42:53 PM</v>
+        <v>7/18/2021, 8:48:25 AM</v>
       </c>
       <c r="M365" t="str">
         <v>Calendar</v>
@@ -23027,57 +23026,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P365" t="str">
-        <v>2021-06-20T00:42:53.876Z</v>
+        <v>2021-07-18T09:48:25.476Z</v>
       </c>
       <c r="Q365" t="str">
-        <v>6/19/2021, 8:42:53 PM</v>
+        <v>7/18/2021, 5:48:25 AM</v>
       </c>
       <c r="R365" t="str">
-        <v>2021-06-20T02:32:53.876Z</v>
+        <v>2021-07-18T10:53:25.476Z</v>
       </c>
       <c r="S365" t="str">
-        <v>6/19/2021, 10:32:53 PM</v>
+        <v>7/18/2021, 6:53:25 AM</v>
       </c>
       <c r="T365">
-        <v>110</v>
+        <v>65</v>
       </c>
     </row>
     <row r="366">
       <c r="A366">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="B366" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C366" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D366" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E366" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F366" t="str">
-        <v>Sticky Which</v>
+        <v>Distributed Towards</v>
       </c>
       <c r="G366" t="str">
-        <v>8124639</v>
+        <v>8008195</v>
       </c>
       <c r="H366" t="str">
         <v/>
       </c>
       <c r="I366" t="str">
-        <v>2022-04-10T08:53:38.723Z</v>
+        <v>2021-07-31T01:59:52.624Z</v>
       </c>
       <c r="J366" t="str">
-        <v>4/10/2022, 4:53:38 AM</v>
+        <v>7/30/2021, 9:59:52 PM</v>
       </c>
       <c r="K366" t="str">
-        <v>2022-04-10T09:53:38.723Z</v>
+        <v>2021-07-31T03:59:52.624Z</v>
       </c>
       <c r="L366" t="str">
-        <v>4/10/2022, 5:53:38 AM</v>
+        <v>7/30/2021, 11:59:52 PM</v>
       </c>
       <c r="M366" t="str">
         <v>Calendar</v>
@@ -23089,57 +23088,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P366" t="str">
-        <v>2022-04-10T08:53:38.723Z</v>
+        <v>2021-07-31T01:59:52.624Z</v>
       </c>
       <c r="Q366" t="str">
-        <v>4/10/2022, 4:53:38 AM</v>
+        <v>7/30/2021, 9:59:52 PM</v>
       </c>
       <c r="R366" t="str">
-        <v>2022-04-10T09:43:38.723Z</v>
+        <v>2021-07-31T02:54:52.624Z</v>
       </c>
       <c r="S366" t="str">
-        <v>4/10/2022, 5:43:38 AM</v>
+        <v>7/30/2021, 10:54:52 PM</v>
       </c>
       <c r="T366">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="367">
       <c r="A367">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="B367" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C367" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D367" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E367" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F367" t="str">
-        <v>Impactful Yuck Via</v>
+        <v>World-Class Down Ouch</v>
       </c>
       <c r="G367" t="str">
-        <v>6452102</v>
+        <v>8907246</v>
       </c>
       <c r="H367" t="str">
         <v/>
       </c>
       <c r="I367" t="str">
-        <v>2022-05-12T04:19:37.907Z</v>
+        <v>2021-08-27T06:16:52.450Z</v>
       </c>
       <c r="J367" t="str">
-        <v>5/12/2022, 12:19:37 AM</v>
+        <v>8/27/2021, 2:16:52 AM</v>
       </c>
       <c r="K367" t="str">
-        <v>2022-05-12T06:19:37.907Z</v>
+        <v>2021-08-27T10:16:52.450Z</v>
       </c>
       <c r="L367" t="str">
-        <v>5/12/2022, 2:19:37 AM</v>
+        <v>8/27/2021, 6:16:52 AM</v>
       </c>
       <c r="M367" t="str">
         <v>Calendar</v>
@@ -23151,57 +23150,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P367" t="str">
-        <v>2022-05-12T04:19:37.907Z</v>
+        <v>2021-08-27T06:16:52.450Z</v>
       </c>
       <c r="Q367" t="str">
-        <v>5/12/2022, 12:19:37 AM</v>
+        <v>8/27/2021, 2:16:52 AM</v>
       </c>
       <c r="R367" t="str">
-        <v>2022-05-12T05:23:37.907Z</v>
+        <v>2021-08-27T08:23:52.450Z</v>
       </c>
       <c r="S367" t="str">
-        <v>5/12/2022, 1:23:37 AM</v>
+        <v>8/27/2021, 4:23:52 AM</v>
       </c>
       <c r="T367">
-        <v>64</v>
+        <v>127</v>
       </c>
     </row>
     <row r="368">
       <c r="A368">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="B368" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C368" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D368" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E368" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F368" t="str">
-        <v>Best-Of-Breed Hopelessly Gracious</v>
+        <v>World-Class Kick</v>
       </c>
       <c r="G368" t="str">
-        <v>1895485</v>
+        <v>9410866</v>
       </c>
       <c r="H368" t="str">
-        <v/>
+        <v>ZD142950</v>
       </c>
       <c r="I368" t="str">
-        <v>2022-05-19T20:48:04.893Z</v>
+        <v>2021-10-03T11:09:40.153Z</v>
       </c>
       <c r="J368" t="str">
-        <v>5/19/2022, 4:48:04 PM</v>
+        <v>10/3/2021, 7:09:40 AM</v>
       </c>
       <c r="K368" t="str">
-        <v>2022-05-20T00:48:04.893Z</v>
+        <v>2021-10-03T15:09:40.153Z</v>
       </c>
       <c r="L368" t="str">
-        <v>5/19/2022, 8:48:04 PM</v>
+        <v>10/3/2021, 11:09:40 AM</v>
       </c>
       <c r="M368" t="str">
         <v>Calendar</v>
@@ -23213,57 +23212,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P368" t="str">
-        <v>2022-05-19T20:48:04.893Z</v>
+        <v>2021-10-03T11:09:40.153Z</v>
       </c>
       <c r="Q368" t="str">
-        <v>5/19/2022, 4:48:04 PM</v>
+        <v>10/3/2021, 7:09:40 AM</v>
       </c>
       <c r="R368" t="str">
-        <v>2022-05-19T22:40:04.893Z</v>
+        <v>2021-10-03T13:49:40.153Z</v>
       </c>
       <c r="S368" t="str">
-        <v>5/19/2022, 6:40:04 PM</v>
+        <v>10/3/2021, 9:49:40 AM</v>
       </c>
       <c r="T368">
-        <v>112</v>
+        <v>160</v>
       </c>
     </row>
     <row r="369">
       <c r="A369">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="B369" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C369" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D369" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E369" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F369" t="str">
-        <v>Mission-Critical Below King</v>
+        <v>Best-Of-Breed Firm Muddy</v>
       </c>
       <c r="G369" t="str">
-        <v>1503395</v>
+        <v>9021727</v>
       </c>
       <c r="H369" t="str">
-        <v/>
+        <v>ZD954701</v>
       </c>
       <c r="I369" t="str">
-        <v>2022-08-08T05:58:26.201Z</v>
+        <v>2021-10-04T20:52:38.319Z</v>
       </c>
       <c r="J369" t="str">
-        <v>8/8/2022, 1:58:26 AM</v>
+        <v>10/4/2021, 4:52:38 PM</v>
       </c>
       <c r="K369" t="str">
-        <v>2022-08-08T09:58:26.201Z</v>
+        <v>2021-10-04T23:52:38.319Z</v>
       </c>
       <c r="L369" t="str">
-        <v>8/8/2022, 5:58:26 AM</v>
+        <v>10/4/2021, 7:52:38 PM</v>
       </c>
       <c r="M369" t="str">
         <v>Calendar</v>
@@ -23275,57 +23274,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P369" t="str">
-        <v>2022-08-08T05:58:26.201Z</v>
+        <v>2021-10-04T20:52:38.319Z</v>
       </c>
       <c r="Q369" t="str">
-        <v>8/8/2022, 1:58:26 AM</v>
+        <v>10/4/2021, 4:52:38 PM</v>
       </c>
       <c r="R369" t="str">
-        <v>2022-08-08T09:20:26.201Z</v>
+        <v>2021-10-04T23:30:38.319Z</v>
       </c>
       <c r="S369" t="str">
-        <v>8/8/2022, 5:20:26 AM</v>
+        <v>10/4/2021, 7:30:38 PM</v>
       </c>
       <c r="T369">
-        <v>202</v>
+        <v>158</v>
       </c>
     </row>
     <row r="370">
       <c r="A370">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="B370" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C370" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D370" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E370" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F370" t="str">
-        <v>Innovative Via Oof</v>
+        <v>Magnetic Jubilantly Concrete Past</v>
       </c>
       <c r="G370" t="str">
-        <v>1282539</v>
+        <v>7639277</v>
       </c>
       <c r="H370" t="str">
         <v/>
       </c>
       <c r="I370" t="str">
-        <v>2022-12-07T10:20:47.037Z</v>
+        <v>2021-12-25T23:06:28.007Z</v>
       </c>
       <c r="J370" t="str">
-        <v>12/7/2022, 5:20:47 AM</v>
+        <v>12/25/2021, 6:06:28 PM</v>
       </c>
       <c r="K370" t="str">
-        <v>2022-12-07T14:20:47.037Z</v>
+        <v>2021-12-26T01:06:28.007Z</v>
       </c>
       <c r="L370" t="str">
-        <v>12/7/2022, 9:20:47 AM</v>
+        <v>12/25/2021, 8:06:28 PM</v>
       </c>
       <c r="M370" t="str">
         <v>Calendar</v>
@@ -23337,57 +23336,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P370" t="str">
-        <v>2022-12-07T10:20:47.037Z</v>
+        <v>2021-12-25T23:06:28.007Z</v>
       </c>
       <c r="Q370" t="str">
-        <v>12/7/2022, 5:20:47 AM</v>
+        <v>12/25/2021, 6:06:28 PM</v>
       </c>
       <c r="R370" t="str">
-        <v>2022-12-07T11:43:47.037Z</v>
+        <v>2021-12-26T00:32:28.007Z</v>
       </c>
       <c r="S370" t="str">
-        <v>12/7/2022, 6:43:47 AM</v>
+        <v>12/25/2021, 7:32:28 PM</v>
       </c>
       <c r="T370">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="371">
       <c r="A371">
-        <v>280</v>
+        <v>195</v>
       </c>
       <c r="B371" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C371" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D371" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E371" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F371" t="str">
-        <v>Integrated Now Unfortunately Finally</v>
+        <v>B2C Cuddly Refer Sin</v>
       </c>
       <c r="G371" t="str">
-        <v>1514032</v>
+        <v>4332519</v>
       </c>
       <c r="H371" t="str">
-        <v>ZD088506</v>
+        <v/>
       </c>
       <c r="I371" t="str">
-        <v>2023-05-07T01:21:51.191Z</v>
+        <v>2021-12-29T01:05:31.852Z</v>
       </c>
       <c r="J371" t="str">
-        <v>5/6/2023, 9:21:51 PM</v>
+        <v>12/28/2021, 8:05:31 PM</v>
       </c>
       <c r="K371" t="str">
-        <v>2023-05-07T02:21:51.191Z</v>
+        <v>2021-12-29T03:05:31.852Z</v>
       </c>
       <c r="L371" t="str">
-        <v>5/6/2023, 10:21:51 PM</v>
+        <v>12/28/2021, 10:05:31 PM</v>
       </c>
       <c r="M371" t="str">
         <v>Calendar</v>
@@ -23399,57 +23398,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P371" t="str">
-        <v>2023-05-07T01:21:51.191Z</v>
+        <v>2021-12-29T01:05:31.852Z</v>
       </c>
       <c r="Q371" t="str">
-        <v>5/6/2023, 9:21:51 PM</v>
+        <v>12/28/2021, 8:05:31 PM</v>
       </c>
       <c r="R371" t="str">
-        <v>2023-05-07T02:10:51.191Z</v>
+        <v>2021-12-29T02:44:31.852Z</v>
       </c>
       <c r="S371" t="str">
-        <v>5/6/2023, 10:10:51 PM</v>
+        <v>12/28/2021, 9:44:31 PM</v>
       </c>
       <c r="T371">
-        <v>49</v>
+        <v>99</v>
       </c>
     </row>
     <row r="372">
       <c r="A372">
-        <v>281</v>
+        <v>205</v>
       </c>
       <c r="B372" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C372" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D372" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E372" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F372" t="str">
-        <v>One-To-One Yum</v>
+        <v>Collaborative Provided Tightly Toe</v>
       </c>
       <c r="G372" t="str">
-        <v>1095875</v>
+        <v>2481380</v>
       </c>
       <c r="H372" t="str">
-        <v/>
+        <v>ZD623154</v>
       </c>
       <c r="I372" t="str">
-        <v>2023-05-09T10:38:56.764Z</v>
+        <v>2022-03-25T10:53:48.781Z</v>
       </c>
       <c r="J372" t="str">
-        <v>5/9/2023, 6:38:56 AM</v>
+        <v>3/25/2022, 6:53:48 AM</v>
       </c>
       <c r="K372" t="str">
-        <v>2023-05-09T12:38:56.764Z</v>
+        <v>2022-03-25T12:53:48.781Z</v>
       </c>
       <c r="L372" t="str">
-        <v>5/9/2023, 8:38:56 AM</v>
+        <v>3/25/2022, 8:53:48 AM</v>
       </c>
       <c r="M372" t="str">
         <v>Calendar</v>
@@ -23461,57 +23460,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P372" t="str">
-        <v>2023-05-09T10:38:56.764Z</v>
+        <v>2022-03-25T10:53:48.781Z</v>
       </c>
       <c r="Q372" t="str">
-        <v>5/9/2023, 6:38:56 AM</v>
+        <v>3/25/2022, 6:53:48 AM</v>
       </c>
       <c r="R372" t="str">
-        <v>2023-05-09T11:30:56.764Z</v>
+        <v>2022-03-25T12:36:48.781Z</v>
       </c>
       <c r="S372" t="str">
-        <v>5/9/2023, 7:30:56 AM</v>
+        <v>3/25/2022, 8:36:48 AM</v>
       </c>
       <c r="T372">
-        <v>52</v>
+        <v>103</v>
       </c>
     </row>
     <row r="373">
       <c r="A373">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="B373" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C373" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D373" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E373" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F373" t="str">
-        <v>Out-Of-The-Box Glisten Appreciate</v>
+        <v>Synergistic Fail</v>
       </c>
       <c r="G373" t="str">
-        <v>4196463</v>
+        <v>1165545</v>
       </c>
       <c r="H373" t="str">
-        <v>ZD261108</v>
+        <v>ZD858854</v>
       </c>
       <c r="I373" t="str">
-        <v>2023-08-02T22:20:22.482Z</v>
+        <v>2022-07-03T21:12:11.202Z</v>
       </c>
       <c r="J373" t="str">
-        <v>8/2/2023, 6:20:22 PM</v>
+        <v>7/3/2022, 5:12:11 PM</v>
       </c>
       <c r="K373" t="str">
-        <v>2023-08-03T01:20:22.482Z</v>
+        <v>2022-07-03T23:12:11.202Z</v>
       </c>
       <c r="L373" t="str">
-        <v>8/2/2023, 9:20:22 PM</v>
+        <v>7/3/2022, 7:12:11 PM</v>
       </c>
       <c r="M373" t="str">
         <v>Calendar</v>
@@ -23523,57 +23522,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P373" t="str">
-        <v>2023-08-02T22:20:22.482Z</v>
+        <v>2022-07-03T21:12:11.202Z</v>
       </c>
       <c r="Q373" t="str">
-        <v>8/2/2023, 6:20:22 PM</v>
+        <v>7/3/2022, 5:12:11 PM</v>
       </c>
       <c r="R373" t="str">
-        <v>2023-08-02T22:59:22.482Z</v>
+        <v>2022-07-03T21:53:11.202Z</v>
       </c>
       <c r="S373" t="str">
-        <v>8/2/2023, 6:59:22 PM</v>
+        <v>7/3/2022, 5:53:11 PM</v>
       </c>
       <c r="T373">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="374">
       <c r="A374">
-        <v>326</v>
+        <v>232</v>
       </c>
       <c r="B374" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C374" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D374" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E374" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F374" t="str">
-        <v>Interactive Abandoned Fork</v>
+        <v>Plug-And-Play Knight</v>
       </c>
       <c r="G374" t="str">
-        <v>3817938</v>
+        <v>8655283</v>
       </c>
       <c r="H374" t="str">
-        <v>ZD459340</v>
+        <v>ZD239676</v>
       </c>
       <c r="I374" t="str">
-        <v>2024-01-31T18:27:56.360Z</v>
+        <v>2022-08-13T06:28:29.802Z</v>
       </c>
       <c r="J374" t="str">
-        <v>1/31/2024, 1:27:56 PM</v>
+        <v>8/13/2022, 2:28:29 AM</v>
       </c>
       <c r="K374" t="str">
-        <v>2024-01-31T20:27:56.360Z</v>
+        <v>2022-08-13T08:28:29.802Z</v>
       </c>
       <c r="L374" t="str">
-        <v>1/31/2024, 3:27:56 PM</v>
+        <v>8/13/2022, 4:28:29 AM</v>
       </c>
       <c r="M374" t="str">
         <v>Calendar</v>
@@ -23585,57 +23584,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P374" t="str">
-        <v>2024-01-31T18:27:56.360Z</v>
+        <v>2022-08-13T06:28:29.802Z</v>
       </c>
       <c r="Q374" t="str">
-        <v>1/31/2024, 1:27:56 PM</v>
+        <v>8/13/2022, 2:28:29 AM</v>
       </c>
       <c r="R374" t="str">
-        <v>2024-01-31T20:15:56.360Z</v>
+        <v>2022-08-13T07:27:29.802Z</v>
       </c>
       <c r="S374" t="str">
-        <v>1/31/2024, 3:15:56 PM</v>
+        <v>8/13/2022, 3:27:29 AM</v>
       </c>
       <c r="T374">
-        <v>108</v>
+        <v>59</v>
       </c>
     </row>
     <row r="375">
       <c r="A375">
-        <v>330</v>
+        <v>245</v>
       </c>
       <c r="B375" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C375" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D375" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E375" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F375" t="str">
-        <v>End-To-End Psst Scale Potable</v>
+        <v>Open-Source Whoa Scare</v>
       </c>
       <c r="G375" t="str">
-        <v>8250420</v>
+        <v>4800039</v>
       </c>
       <c r="H375" t="str">
-        <v>ZD638232</v>
+        <v/>
       </c>
       <c r="I375" t="str">
-        <v>2024-02-25T10:48:14.703Z</v>
+        <v>2022-10-17T03:51:22.824Z</v>
       </c>
       <c r="J375" t="str">
-        <v>2/25/2024, 5:48:14 AM</v>
+        <v>10/16/2022, 11:51:22 PM</v>
       </c>
       <c r="K375" t="str">
-        <v>2024-02-25T13:48:14.703Z</v>
+        <v>2022-10-17T04:51:22.824Z</v>
       </c>
       <c r="L375" t="str">
-        <v>2/25/2024, 8:48:14 AM</v>
+        <v>10/17/2022, 12:51:22 AM</v>
       </c>
       <c r="M375" t="str">
         <v>Calendar</v>
@@ -23647,57 +23646,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P375" t="str">
-        <v>2024-02-25T10:48:14.703Z</v>
+        <v>2022-10-17T03:51:22.824Z</v>
       </c>
       <c r="Q375" t="str">
-        <v>2/25/2024, 5:48:14 AM</v>
+        <v>10/16/2022, 11:51:22 PM</v>
       </c>
       <c r="R375" t="str">
-        <v>2024-02-25T12:34:14.703Z</v>
+        <v>2022-10-17T04:31:22.824Z</v>
       </c>
       <c r="S375" t="str">
-        <v>2/25/2024, 7:34:14 AM</v>
+        <v>10/17/2022, 12:31:22 AM</v>
       </c>
       <c r="T375">
-        <v>106</v>
+        <v>40</v>
       </c>
     </row>
     <row r="376">
       <c r="A376">
-        <v>354</v>
+        <v>258</v>
       </c>
       <c r="B376" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C376" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D376" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E376" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F376" t="str">
-        <v>Synergistic Sauerkraut</v>
+        <v>Proactive Although</v>
       </c>
       <c r="G376" t="str">
-        <v>1807857</v>
+        <v>3017429</v>
       </c>
       <c r="H376" t="str">
         <v/>
       </c>
       <c r="I376" t="str">
-        <v>2024-06-25T21:53:06.886Z</v>
+        <v>2022-12-18T14:34:20.684Z</v>
       </c>
       <c r="J376" t="str">
-        <v>6/25/2024, 5:53:06 PM</v>
+        <v>12/18/2022, 9:34:20 AM</v>
       </c>
       <c r="K376" t="str">
-        <v>2024-06-26T01:53:06.886Z</v>
+        <v>2022-12-18T17:34:20.684Z</v>
       </c>
       <c r="L376" t="str">
-        <v>6/25/2024, 9:53:06 PM</v>
+        <v>12/18/2022, 12:34:20 PM</v>
       </c>
       <c r="M376" t="str">
         <v>Calendar</v>
@@ -23709,57 +23708,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P376" t="str">
-        <v>2024-06-25T21:53:06.886Z</v>
+        <v>2022-12-18T14:34:20.684Z</v>
       </c>
       <c r="Q376" t="str">
-        <v>6/25/2024, 5:53:06 PM</v>
+        <v>12/18/2022, 9:34:20 AM</v>
       </c>
       <c r="R376" t="str">
-        <v>2024-06-25T23:32:06.886Z</v>
+        <v>2022-12-18T15:44:20.684Z</v>
       </c>
       <c r="S376" t="str">
-        <v>6/25/2024, 7:32:06 PM</v>
+        <v>12/18/2022, 10:44:20 AM</v>
       </c>
       <c r="T376">
-        <v>99</v>
+        <v>70</v>
       </c>
     </row>
     <row r="377">
       <c r="A377">
-        <v>361</v>
+        <v>270</v>
       </c>
       <c r="B377" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C377" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D377" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E377" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F377" t="str">
-        <v>Seamless Provided</v>
+        <v>Best-Of-Breed Between Manner</v>
       </c>
       <c r="G377" t="str">
-        <v>8181010</v>
+        <v>7618409</v>
       </c>
       <c r="H377" t="str">
-        <v>ZD981702</v>
+        <v/>
       </c>
       <c r="I377" t="str">
-        <v>2024-08-19T23:42:33.805Z</v>
+        <v>2023-03-01T01:53:42.807Z</v>
       </c>
       <c r="J377" t="str">
-        <v>8/19/2024, 7:42:33 PM</v>
+        <v>2/28/2023, 8:53:42 PM</v>
       </c>
       <c r="K377" t="str">
-        <v>2024-08-20T02:42:33.805Z</v>
+        <v>2023-03-01T02:53:42.807Z</v>
       </c>
       <c r="L377" t="str">
-        <v>8/19/2024, 10:42:33 PM</v>
+        <v>2/28/2023, 9:53:42 PM</v>
       </c>
       <c r="M377" t="str">
         <v>Calendar</v>
@@ -23771,57 +23770,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P377" t="str">
-        <v>2024-08-19T23:42:33.805Z</v>
+        <v>2023-03-01T01:53:42.807Z</v>
       </c>
       <c r="Q377" t="str">
-        <v>8/19/2024, 7:42:33 PM</v>
+        <v>2/28/2023, 8:53:42 PM</v>
       </c>
       <c r="R377" t="str">
-        <v>2024-08-20T02:21:33.805Z</v>
+        <v>2023-03-01T02:24:42.807Z</v>
       </c>
       <c r="S377" t="str">
-        <v>8/19/2024, 10:21:33 PM</v>
+        <v>2/28/2023, 9:24:42 PM</v>
       </c>
       <c r="T377">
-        <v>159</v>
+        <v>31</v>
       </c>
     </row>
     <row r="378">
       <c r="A378">
-        <v>390</v>
+        <v>290</v>
       </c>
       <c r="B378" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C378" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D378" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E378" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F378" t="str">
-        <v>B2C Masquerade</v>
+        <v>Best-Of-Breed Bestride Than</v>
       </c>
       <c r="G378" t="str">
-        <v>6093737</v>
+        <v>1357785</v>
       </c>
       <c r="H378" t="str">
-        <v/>
+        <v>ZD858960</v>
       </c>
       <c r="I378" t="str">
-        <v>2025-02-28T03:10:22.755Z</v>
+        <v>2023-07-31T02:37:43.247Z</v>
       </c>
       <c r="J378" t="str">
-        <v>2/27/2025, 10:10:22 PM</v>
+        <v>7/30/2023, 10:37:43 PM</v>
       </c>
       <c r="K378" t="str">
-        <v>2025-02-28T07:10:22.755Z</v>
+        <v>2023-07-31T05:37:43.247Z</v>
       </c>
       <c r="L378" t="str">
-        <v>2/28/2025, 2:10:22 AM</v>
+        <v>7/31/2023, 1:37:43 AM</v>
       </c>
       <c r="M378" t="str">
         <v>Calendar</v>
@@ -23833,57 +23832,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P378" t="str">
-        <v>2025-02-28T03:10:22.755Z</v>
+        <v>2023-07-31T02:37:43.247Z</v>
       </c>
       <c r="Q378" t="str">
-        <v>2/27/2025, 10:10:22 PM</v>
+        <v>7/30/2023, 10:37:43 PM</v>
       </c>
       <c r="R378" t="str">
-        <v>2025-02-28T05:45:22.755Z</v>
+        <v>2023-07-31T05:33:43.247Z</v>
       </c>
       <c r="S378" t="str">
-        <v>2/28/2025, 12:45:22 AM</v>
+        <v>7/31/2023, 1:33:43 AM</v>
       </c>
       <c r="T378">
-        <v>155</v>
+        <v>176</v>
       </c>
     </row>
     <row r="379">
       <c r="A379">
-        <v>406</v>
+        <v>338</v>
       </c>
       <c r="B379" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C379" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D379" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E379" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F379" t="str">
-        <v>Extensible Retrospectivity</v>
+        <v>Customized Jittery</v>
       </c>
       <c r="G379" t="str">
-        <v>8578458</v>
+        <v>2986821</v>
       </c>
       <c r="H379" t="str">
-        <v>ZD837236</v>
+        <v/>
       </c>
       <c r="I379" t="str">
-        <v>2025-05-29T00:12:48.889Z</v>
+        <v>2024-04-07T13:56:58.000Z</v>
       </c>
       <c r="J379" t="str">
-        <v>5/28/2025, 8:12:48 PM</v>
+        <v>4/7/2024, 9:56:58 AM</v>
       </c>
       <c r="K379" t="str">
-        <v>2025-05-29T04:12:48.889Z</v>
+        <v>2024-04-07T14:56:58.000Z</v>
       </c>
       <c r="L379" t="str">
-        <v>5/29/2025, 12:12:48 AM</v>
+        <v>4/7/2024, 10:56:58 AM</v>
       </c>
       <c r="M379" t="str">
         <v>Calendar</v>
@@ -23895,57 +23894,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P379" t="str">
-        <v>2025-05-29T00:12:48.889Z</v>
+        <v>2024-04-07T13:56:58.000Z</v>
       </c>
       <c r="Q379" t="str">
-        <v>5/28/2025, 8:12:48 PM</v>
+        <v>4/7/2024, 9:56:58 AM</v>
       </c>
       <c r="R379" t="str">
-        <v>2025-05-29T01:37:48.889Z</v>
+        <v>2024-04-07T14:53:58.000Z</v>
       </c>
       <c r="S379" t="str">
-        <v>5/28/2025, 9:37:48 PM</v>
+        <v>4/7/2024, 10:53:58 AM</v>
       </c>
       <c r="T379">
-        <v>85</v>
+        <v>57</v>
       </c>
     </row>
     <row r="380">
       <c r="A380">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="B380" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C380" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D380" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E380" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F380" t="str">
-        <v>Back-End Numeric</v>
+        <v>Interactive Towards Scary Spark</v>
       </c>
       <c r="G380" t="str">
-        <v>5140781</v>
+        <v>9580649</v>
       </c>
       <c r="H380" t="str">
-        <v>ZD297884</v>
+        <v>ZD605972</v>
       </c>
       <c r="I380" t="str">
-        <v>2025-06-10T02:56:47.250Z</v>
+        <v>2024-04-19T23:56:39.254Z</v>
       </c>
       <c r="J380" t="str">
-        <v>6/9/2025, 10:56:47 PM</v>
+        <v>4/19/2024, 7:56:39 PM</v>
       </c>
       <c r="K380" t="str">
-        <v>2025-06-10T04:56:47.250Z</v>
+        <v>2024-04-20T02:56:39.254Z</v>
       </c>
       <c r="L380" t="str">
-        <v>6/10/2025, 12:56:47 AM</v>
+        <v>4/19/2024, 10:56:39 PM</v>
       </c>
       <c r="M380" t="str">
         <v>Calendar</v>
@@ -23957,57 +23956,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P380" t="str">
-        <v>2025-06-10T02:56:47.250Z</v>
+        <v>2024-04-19T23:56:39.254Z</v>
       </c>
       <c r="Q380" t="str">
-        <v>6/9/2025, 10:56:47 PM</v>
+        <v>4/19/2024, 7:56:39 PM</v>
       </c>
       <c r="R380" t="str">
-        <v>2025-06-10T03:51:47.250Z</v>
+        <v>2024-04-20T01:47:39.254Z</v>
       </c>
       <c r="S380" t="str">
-        <v>6/9/2025, 11:51:47 PM</v>
+        <v>4/19/2024, 9:47:39 PM</v>
       </c>
       <c r="T380">
-        <v>55</v>
+        <v>111</v>
       </c>
     </row>
     <row r="381">
       <c r="A381">
-        <v>417</v>
+        <v>342</v>
       </c>
       <c r="B381" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C381" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D381" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E381" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F381" t="str">
-        <v>One-To-One Impossible Crumble Affectionate</v>
+        <v>Leading-Edge Instead Onto</v>
       </c>
       <c r="G381" t="str">
-        <v>5783731</v>
+        <v>8219162</v>
       </c>
       <c r="H381" t="str">
         <v/>
       </c>
       <c r="I381" t="str">
-        <v>2025-07-03T08:17:13.878Z</v>
+        <v>2024-04-20T20:35:33.201Z</v>
       </c>
       <c r="J381" t="str">
-        <v>7/3/2025, 4:17:13 AM</v>
+        <v>4/20/2024, 4:35:33 PM</v>
       </c>
       <c r="K381" t="str">
-        <v>2025-07-03T09:17:13.878Z</v>
+        <v>2024-04-21T00:35:33.201Z</v>
       </c>
       <c r="L381" t="str">
-        <v>7/3/2025, 5:17:13 AM</v>
+        <v>4/20/2024, 8:35:33 PM</v>
       </c>
       <c r="M381" t="str">
         <v>Calendar</v>
@@ -24019,57 +24018,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P381" t="str">
-        <v>2025-07-03T08:17:13.878Z</v>
+        <v>2024-04-20T20:35:33.201Z</v>
       </c>
       <c r="Q381" t="str">
-        <v>7/3/2025, 4:17:13 AM</v>
+        <v>4/20/2024, 4:35:33 PM</v>
       </c>
       <c r="R381" t="str">
-        <v>2025-07-03T09:07:13.878Z</v>
+        <v>2024-04-20T23:49:33.201Z</v>
       </c>
       <c r="S381" t="str">
-        <v>7/3/2025, 5:07:13 AM</v>
+        <v>4/20/2024, 7:49:33 PM</v>
       </c>
       <c r="T381">
-        <v>50</v>
+        <v>194</v>
       </c>
     </row>
     <row r="382">
       <c r="A382">
-        <v>423</v>
+        <v>359</v>
       </c>
       <c r="B382" t="str">
-        <v>Miller Mayert</v>
+        <v>Morgan Johnson</v>
       </c>
       <c r="C382" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="D382" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
+        <v>admin-morganjohnson-2@fgcu.local</v>
       </c>
       <c r="E382" t="str">
-        <v>4456102911</v>
+        <v>6607887497</v>
       </c>
       <c r="F382" t="str">
-        <v>Back-End Loftily Horn Noteworthy</v>
+        <v>User-Centric Upon Quick</v>
       </c>
       <c r="G382" t="str">
-        <v>7432112</v>
+        <v>3358770</v>
       </c>
       <c r="H382" t="str">
-        <v>ZD599982</v>
+        <v>ZD706372</v>
       </c>
       <c r="I382" t="str">
-        <v>2025-08-03T06:39:16.333Z</v>
+        <v>2024-07-03T19:05:35.333Z</v>
       </c>
       <c r="J382" t="str">
-        <v>8/3/2025, 2:39:16 AM</v>
+        <v>7/3/2024, 3:05:35 PM</v>
       </c>
       <c r="K382" t="str">
-        <v>2025-08-03T09:39:16.333Z</v>
+        <v>2024-07-03T23:05:35.333Z</v>
       </c>
       <c r="L382" t="str">
-        <v>8/3/2025, 5:39:16 AM</v>
+        <v>7/3/2024, 7:05:35 PM</v>
       </c>
       <c r="M382" t="str">
         <v>Calendar</v>
@@ -24081,24 +24080,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P382" t="str">
-        <v>2025-08-03T06:39:16.333Z</v>
+        <v>2024-07-03T19:05:35.333Z</v>
       </c>
       <c r="Q382" t="str">
-        <v>8/3/2025, 2:39:16 AM</v>
+        <v>7/3/2024, 3:05:35 PM</v>
       </c>
       <c r="R382" t="str">
-        <v>2025-08-03T08:22:16.333Z</v>
+        <v>2024-07-03T20:56:35.333Z</v>
       </c>
       <c r="S382" t="str">
-        <v>8/3/2025, 4:22:16 AM</v>
+        <v>7/3/2024, 4:56:35 PM</v>
       </c>
       <c r="T382">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="383">
       <c r="A383">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="B383" t="str">
         <v>Morgan Johnson</v>
@@ -24113,25 +24112,25 @@
         <v>6607887497</v>
       </c>
       <c r="F383" t="str">
-        <v>Visionary Supportive Carefree Unto</v>
+        <v>AI-Driven Over Loftily</v>
       </c>
       <c r="G383" t="str">
-        <v>6504796</v>
+        <v>3052879</v>
       </c>
       <c r="H383" t="str">
-        <v>ZD075695</v>
+        <v>ZD408733</v>
       </c>
       <c r="I383" t="str">
-        <v>2019-02-16T11:08:22.059Z</v>
+        <v>2024-12-19T10:49:24.776Z</v>
       </c>
       <c r="J383" t="str">
-        <v>2/16/2019, 6:08:22 AM</v>
+        <v>12/19/2024, 5:49:24 AM</v>
       </c>
       <c r="K383" t="str">
-        <v>2019-02-16T12:08:22.059Z</v>
+        <v>2024-12-19T11:49:24.776Z</v>
       </c>
       <c r="L383" t="str">
-        <v>2/16/2019, 7:08:22 AM</v>
+        <v>12/19/2024, 6:49:24 AM</v>
       </c>
       <c r="M383" t="str">
         <v>Calendar</v>
@@ -24143,24 +24142,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P383" t="str">
-        <v>2019-02-16T11:08:22.059Z</v>
+        <v>2024-12-19T10:49:24.776Z</v>
       </c>
       <c r="Q383" t="str">
-        <v>2/16/2019, 6:08:22 AM</v>
+        <v>12/19/2024, 5:49:24 AM</v>
       </c>
       <c r="R383" t="str">
-        <v>2019-02-16T12:05:22.059Z</v>
+        <v>2024-12-19T11:38:24.776Z</v>
       </c>
       <c r="S383" t="str">
-        <v>2/16/2019, 7:05:22 AM</v>
+        <v>12/19/2024, 6:38:24 AM</v>
       </c>
       <c r="T383">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="384">
       <c r="A384">
-        <v>17</v>
+        <v>382</v>
       </c>
       <c r="B384" t="str">
         <v>Morgan Johnson</v>
@@ -24175,25 +24174,25 @@
         <v>6607887497</v>
       </c>
       <c r="F384" t="str">
-        <v>Cutting-Edge Approximate Instead Front</v>
+        <v>Real-Time Mostly Little</v>
       </c>
       <c r="G384" t="str">
-        <v>2742534</v>
+        <v>4768999</v>
       </c>
       <c r="H384" t="str">
         <v/>
       </c>
       <c r="I384" t="str">
-        <v>2019-03-27T05:02:23.316Z</v>
+        <v>2025-01-12T12:41:34.835Z</v>
       </c>
       <c r="J384" t="str">
-        <v>3/27/2019, 1:02:23 AM</v>
+        <v>1/12/2025, 7:41:34 AM</v>
       </c>
       <c r="K384" t="str">
-        <v>2019-03-27T08:02:23.316Z</v>
+        <v>2025-01-12T14:41:34.835Z</v>
       </c>
       <c r="L384" t="str">
-        <v>3/27/2019, 4:02:23 AM</v>
+        <v>1/12/2025, 9:41:34 AM</v>
       </c>
       <c r="M384" t="str">
         <v>Calendar</v>
@@ -24205,24 +24204,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P384" t="str">
-        <v>2019-03-27T05:02:23.316Z</v>
+        <v>2025-01-12T12:41:34.835Z</v>
       </c>
       <c r="Q384" t="str">
-        <v>3/27/2019, 1:02:23 AM</v>
+        <v>1/12/2025, 7:41:34 AM</v>
       </c>
       <c r="R384" t="str">
-        <v>2019-03-27T07:47:23.316Z</v>
+        <v>2025-01-12T14:10:34.835Z</v>
       </c>
       <c r="S384" t="str">
-        <v>3/27/2019, 3:47:23 AM</v>
+        <v>1/12/2025, 9:10:34 AM</v>
       </c>
       <c r="T384">
-        <v>165</v>
+        <v>89</v>
       </c>
     </row>
     <row r="385">
       <c r="A385">
-        <v>24</v>
+        <v>442</v>
       </c>
       <c r="B385" t="str">
         <v>Morgan Johnson</v>
@@ -24237,25 +24236,25 @@
         <v>6607887497</v>
       </c>
       <c r="F385" t="str">
-        <v>Granular Furthermore</v>
+        <v>Compelling Wavy</v>
       </c>
       <c r="G385" t="str">
-        <v>3402553</v>
+        <v>9233048</v>
       </c>
       <c r="H385" t="str">
-        <v/>
+        <v>ZD717770</v>
       </c>
       <c r="I385" t="str">
-        <v>2019-05-11T22:23:52.836Z</v>
+        <v>2025-12-05T15:45:24.288Z</v>
       </c>
       <c r="J385" t="str">
-        <v>5/11/2019, 6:23:52 PM</v>
+        <v>12/5/2025, 10:45:24 AM</v>
       </c>
       <c r="K385" t="str">
-        <v>2019-05-12T01:23:52.836Z</v>
+        <v>2025-12-05T19:45:24.288Z</v>
       </c>
       <c r="L385" t="str">
-        <v>5/11/2019, 9:23:52 PM</v>
+        <v>12/5/2025, 2:45:24 PM</v>
       </c>
       <c r="M385" t="str">
         <v>Calendar</v>
@@ -24267,57 +24266,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P385" t="str">
-        <v>2019-05-11T22:23:52.836Z</v>
+        <v>2025-12-05T15:45:24.288Z</v>
       </c>
       <c r="Q385" t="str">
-        <v>5/11/2019, 6:23:52 PM</v>
+        <v>12/5/2025, 10:45:24 AM</v>
       </c>
       <c r="R385" t="str">
-        <v>2019-05-11T23:01:52.836Z</v>
+        <v>2025-12-05T16:43:24.288Z</v>
       </c>
       <c r="S385" t="str">
-        <v>5/11/2019, 7:01:52 PM</v>
+        <v>12/5/2025, 11:43:24 AM</v>
       </c>
       <c r="T385">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="386">
       <c r="A386">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="B386" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C386" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D386" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E386" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F386" t="str">
-        <v>Proactive Suitcase As Before</v>
+        <v>Frictionless Since</v>
       </c>
       <c r="G386" t="str">
-        <v>7065660</v>
+        <v>6252695</v>
       </c>
       <c r="H386" t="str">
-        <v>ZD399054</v>
+        <v/>
       </c>
       <c r="I386" t="str">
-        <v>2019-12-17T00:23:11.207Z</v>
+        <v>2019-09-19T23:26:13.453Z</v>
       </c>
       <c r="J386" t="str">
-        <v>12/16/2019, 7:23:11 PM</v>
+        <v>9/19/2019, 7:26:13 PM</v>
       </c>
       <c r="K386" t="str">
-        <v>2019-12-17T03:23:11.207Z</v>
+        <v>2019-09-20T03:26:13.453Z</v>
       </c>
       <c r="L386" t="str">
-        <v>12/16/2019, 10:23:11 PM</v>
+        <v>9/19/2019, 11:26:13 PM</v>
       </c>
       <c r="M386" t="str">
         <v>Calendar</v>
@@ -24329,57 +24328,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P386" t="str">
-        <v>2019-12-17T00:23:11.207Z</v>
+        <v>2019-09-19T23:26:13.453Z</v>
       </c>
       <c r="Q386" t="str">
-        <v>12/16/2019, 7:23:11 PM</v>
+        <v>9/19/2019, 7:26:13 PM</v>
       </c>
       <c r="R386" t="str">
-        <v>2019-12-17T02:13:11.207Z</v>
+        <v>2019-09-20T02:56:13.453Z</v>
       </c>
       <c r="S386" t="str">
-        <v>12/16/2019, 9:13:11 PM</v>
+        <v>9/19/2019, 10:56:13 PM</v>
       </c>
       <c r="T386">
-        <v>110</v>
+        <v>210</v>
       </c>
     </row>
     <row r="387">
       <c r="A387">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="B387" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C387" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D387" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E387" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F387" t="str">
-        <v>Proactive Euphonium Blindly As</v>
+        <v>Customized Very Painfully Furthermore</v>
       </c>
       <c r="G387" t="str">
-        <v>1105604</v>
+        <v>5149801</v>
       </c>
       <c r="H387" t="str">
-        <v/>
+        <v>ZD673155</v>
       </c>
       <c r="I387" t="str">
-        <v>2020-04-20T13:22:35.416Z</v>
+        <v>2019-09-28T03:05:58.091Z</v>
       </c>
       <c r="J387" t="str">
-        <v>4/20/2020, 9:22:35 AM</v>
+        <v>9/27/2019, 11:05:58 PM</v>
       </c>
       <c r="K387" t="str">
-        <v>2020-04-20T15:22:35.416Z</v>
+        <v>2019-09-28T07:05:58.091Z</v>
       </c>
       <c r="L387" t="str">
-        <v>4/20/2020, 11:22:35 AM</v>
+        <v>9/28/2019, 3:05:58 AM</v>
       </c>
       <c r="M387" t="str">
         <v>Calendar</v>
@@ -24391,57 +24390,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P387" t="str">
-        <v>2020-04-20T13:22:35.416Z</v>
+        <v>2019-09-28T03:05:58.091Z</v>
       </c>
       <c r="Q387" t="str">
-        <v>4/20/2020, 9:22:35 AM</v>
+        <v>9/27/2019, 11:05:58 PM</v>
       </c>
       <c r="R387" t="str">
-        <v>2020-04-20T14:15:35.416Z</v>
+        <v>2019-09-28T03:46:58.091Z</v>
       </c>
       <c r="S387" t="str">
-        <v>4/20/2020, 10:15:35 AM</v>
+        <v>9/27/2019, 11:46:58 PM</v>
       </c>
       <c r="T387">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="388">
       <c r="A388">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="B388" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C388" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D388" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E388" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F388" t="str">
-        <v>AI-Driven Cantaloupe And Dissemble</v>
+        <v>Customized Enthusiastically Aw</v>
       </c>
       <c r="G388" t="str">
-        <v>6870326</v>
+        <v>5957300</v>
       </c>
       <c r="H388" t="str">
         <v/>
       </c>
       <c r="I388" t="str">
-        <v>2020-05-25T17:54:31.159Z</v>
+        <v>2019-10-14T11:41:20.403Z</v>
       </c>
       <c r="J388" t="str">
-        <v>5/25/2020, 1:54:31 PM</v>
+        <v>10/14/2019, 7:41:20 AM</v>
       </c>
       <c r="K388" t="str">
-        <v>2020-05-25T20:54:31.159Z</v>
+        <v>2019-10-14T13:41:20.403Z</v>
       </c>
       <c r="L388" t="str">
-        <v>5/25/2020, 4:54:31 PM</v>
+        <v>10/14/2019, 9:41:20 AM</v>
       </c>
       <c r="M388" t="str">
         <v>Calendar</v>
@@ -24453,57 +24452,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P388" t="str">
-        <v>2020-05-25T17:54:31.159Z</v>
+        <v>2019-10-14T11:41:20.403Z</v>
       </c>
       <c r="Q388" t="str">
-        <v>5/25/2020, 1:54:31 PM</v>
+        <v>10/14/2019, 7:41:20 AM</v>
       </c>
       <c r="R388" t="str">
-        <v>2020-05-25T18:26:31.159Z</v>
+        <v>2019-10-14T13:41:20.403Z</v>
       </c>
       <c r="S388" t="str">
-        <v>5/25/2020, 2:26:31 PM</v>
+        <v>10/14/2019, 9:41:20 AM</v>
       </c>
       <c r="T388">
-        <v>32</v>
+        <v>120</v>
       </c>
     </row>
     <row r="389">
       <c r="A389">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="B389" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C389" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D389" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E389" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F389" t="str">
-        <v>End-To-End Irk</v>
+        <v>One-To-One Verify Eek</v>
       </c>
       <c r="G389" t="str">
-        <v>8196665</v>
+        <v>6433652</v>
       </c>
       <c r="H389" t="str">
-        <v/>
+        <v>ZD386532</v>
       </c>
       <c r="I389" t="str">
-        <v>2020-07-29T09:50:52.438Z</v>
+        <v>2019-12-06T11:32:21.401Z</v>
       </c>
       <c r="J389" t="str">
-        <v>7/29/2020, 5:50:52 AM</v>
+        <v>12/6/2019, 6:32:21 AM</v>
       </c>
       <c r="K389" t="str">
-        <v>2020-07-29T10:50:52.438Z</v>
+        <v>2019-12-06T13:32:21.401Z</v>
       </c>
       <c r="L389" t="str">
-        <v>7/29/2020, 6:50:52 AM</v>
+        <v>12/6/2019, 8:32:21 AM</v>
       </c>
       <c r="M389" t="str">
         <v>Calendar</v>
@@ -24515,57 +24514,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P389" t="str">
-        <v>2020-07-29T09:50:52.438Z</v>
+        <v>2019-12-06T11:32:21.401Z</v>
       </c>
       <c r="Q389" t="str">
-        <v>7/29/2020, 5:50:52 AM</v>
+        <v>12/6/2019, 6:32:21 AM</v>
       </c>
       <c r="R389" t="str">
-        <v>2020-07-29T10:37:52.438Z</v>
+        <v>2019-12-06T12:14:21.401Z</v>
       </c>
       <c r="S389" t="str">
-        <v>7/29/2020, 6:37:52 AM</v>
+        <v>12/6/2019, 7:14:21 AM</v>
       </c>
       <c r="T389">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="390">
       <c r="A390">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="B390" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C390" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D390" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E390" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F390" t="str">
-        <v>Dynamic Cautious</v>
+        <v>Bleeding-Edge Incidentally Secondary</v>
       </c>
       <c r="G390" t="str">
-        <v>3434194</v>
+        <v>7350535</v>
       </c>
       <c r="H390" t="str">
         <v/>
       </c>
       <c r="I390" t="str">
-        <v>2020-09-10T14:37:44.794Z</v>
+        <v>2020-03-26T03:42:03.701Z</v>
       </c>
       <c r="J390" t="str">
-        <v>9/10/2020, 10:37:44 AM</v>
+        <v>3/25/2020, 11:42:03 PM</v>
       </c>
       <c r="K390" t="str">
-        <v>2020-09-10T17:37:44.794Z</v>
+        <v>2020-03-26T07:42:03.701Z</v>
       </c>
       <c r="L390" t="str">
-        <v>9/10/2020, 1:37:44 PM</v>
+        <v>3/26/2020, 3:42:03 AM</v>
       </c>
       <c r="M390" t="str">
         <v>Calendar</v>
@@ -24577,57 +24576,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P390" t="str">
-        <v>2020-09-10T14:37:44.794Z</v>
+        <v>2020-03-26T03:42:03.701Z</v>
       </c>
       <c r="Q390" t="str">
-        <v>9/10/2020, 10:37:44 AM</v>
+        <v>3/25/2020, 11:42:03 PM</v>
       </c>
       <c r="R390" t="str">
-        <v>2020-09-10T17:19:44.794Z</v>
+        <v>2020-03-26T05:36:03.701Z</v>
       </c>
       <c r="S390" t="str">
-        <v>9/10/2020, 1:19:44 PM</v>
+        <v>3/26/2020, 1:36:03 AM</v>
       </c>
       <c r="T390">
-        <v>162</v>
+        <v>114</v>
       </c>
     </row>
     <row r="391">
       <c r="A391">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="B391" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C391" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D391" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E391" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F391" t="str">
-        <v>Killer Till Monthly Ick</v>
+        <v>Smart Jellyfish</v>
       </c>
       <c r="G391" t="str">
-        <v>7069792</v>
+        <v>5821375</v>
       </c>
       <c r="H391" t="str">
-        <v/>
+        <v>ZD098142</v>
       </c>
       <c r="I391" t="str">
-        <v>2021-07-18T09:48:25.476Z</v>
+        <v>2020-05-31T09:05:45.504Z</v>
       </c>
       <c r="J391" t="str">
-        <v>7/18/2021, 5:48:25 AM</v>
+        <v>5/31/2020, 5:05:45 AM</v>
       </c>
       <c r="K391" t="str">
-        <v>2021-07-18T12:48:25.476Z</v>
+        <v>2020-05-31T10:05:45.504Z</v>
       </c>
       <c r="L391" t="str">
-        <v>7/18/2021, 8:48:25 AM</v>
+        <v>5/31/2020, 6:05:45 AM</v>
       </c>
       <c r="M391" t="str">
         <v>Calendar</v>
@@ -24639,57 +24638,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P391" t="str">
-        <v>2021-07-18T09:48:25.476Z</v>
+        <v>2020-05-31T09:05:45.504Z</v>
       </c>
       <c r="Q391" t="str">
-        <v>7/18/2021, 5:48:25 AM</v>
+        <v>5/31/2020, 5:05:45 AM</v>
       </c>
       <c r="R391" t="str">
-        <v>2021-07-18T10:53:25.476Z</v>
+        <v>2020-05-31T10:03:45.504Z</v>
       </c>
       <c r="S391" t="str">
-        <v>7/18/2021, 6:53:25 AM</v>
+        <v>5/31/2020, 6:03:45 AM</v>
       </c>
       <c r="T391">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="392">
       <c r="A392">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="B392" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C392" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D392" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E392" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F392" t="str">
-        <v>Distributed Towards</v>
+        <v>User-Centric Grimy Frugal Mmm</v>
       </c>
       <c r="G392" t="str">
-        <v>8008195</v>
+        <v>2012145</v>
       </c>
       <c r="H392" t="str">
         <v/>
       </c>
       <c r="I392" t="str">
-        <v>2021-07-31T01:59:52.624Z</v>
+        <v>2020-06-01T20:26:11.191Z</v>
       </c>
       <c r="J392" t="str">
-        <v>7/30/2021, 9:59:52 PM</v>
+        <v>6/1/2020, 4:26:11 PM</v>
       </c>
       <c r="K392" t="str">
-        <v>2021-07-31T03:59:52.624Z</v>
+        <v>2020-06-01T23:26:11.191Z</v>
       </c>
       <c r="L392" t="str">
-        <v>7/30/2021, 11:59:52 PM</v>
+        <v>6/1/2020, 7:26:11 PM</v>
       </c>
       <c r="M392" t="str">
         <v>Calendar</v>
@@ -24701,57 +24700,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P392" t="str">
-        <v>2021-07-31T01:59:52.624Z</v>
+        <v>2020-06-01T20:26:11.191Z</v>
       </c>
       <c r="Q392" t="str">
-        <v>7/30/2021, 9:59:52 PM</v>
+        <v>6/1/2020, 4:26:11 PM</v>
       </c>
       <c r="R392" t="str">
-        <v>2021-07-31T02:54:52.624Z</v>
+        <v>2020-06-01T22:00:11.191Z</v>
       </c>
       <c r="S392" t="str">
-        <v>7/30/2021, 10:54:52 PM</v>
+        <v>6/1/2020, 6:00:11 PM</v>
       </c>
       <c r="T392">
-        <v>55</v>
+        <v>94</v>
       </c>
     </row>
     <row r="393">
       <c r="A393">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="B393" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C393" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D393" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E393" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F393" t="str">
-        <v>World-Class Down Ouch</v>
+        <v>Scalable Via Vague</v>
       </c>
       <c r="G393" t="str">
-        <v>8907246</v>
+        <v>8803570</v>
       </c>
       <c r="H393" t="str">
-        <v/>
+        <v>ZD498764</v>
       </c>
       <c r="I393" t="str">
-        <v>2021-08-27T06:16:52.450Z</v>
+        <v>2021-04-07T05:25:54.418Z</v>
       </c>
       <c r="J393" t="str">
-        <v>8/27/2021, 2:16:52 AM</v>
+        <v>4/7/2021, 1:25:54 AM</v>
       </c>
       <c r="K393" t="str">
-        <v>2021-08-27T10:16:52.450Z</v>
+        <v>2021-04-07T06:25:54.418Z</v>
       </c>
       <c r="L393" t="str">
-        <v>8/27/2021, 6:16:52 AM</v>
+        <v>4/7/2021, 2:25:54 AM</v>
       </c>
       <c r="M393" t="str">
         <v>Calendar</v>
@@ -24763,57 +24762,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P393" t="str">
-        <v>2021-08-27T06:16:52.450Z</v>
+        <v>2021-04-07T05:25:54.418Z</v>
       </c>
       <c r="Q393" t="str">
-        <v>8/27/2021, 2:16:52 AM</v>
+        <v>4/7/2021, 1:25:54 AM</v>
       </c>
       <c r="R393" t="str">
-        <v>2021-08-27T08:23:52.450Z</v>
+        <v>2021-04-07T05:58:54.418Z</v>
       </c>
       <c r="S393" t="str">
-        <v>8/27/2021, 4:23:52 AM</v>
+        <v>4/7/2021, 1:58:54 AM</v>
       </c>
       <c r="T393">
-        <v>127</v>
+        <v>33</v>
       </c>
     </row>
     <row r="394">
       <c r="A394">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="B394" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C394" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D394" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E394" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F394" t="str">
-        <v>World-Class Kick</v>
+        <v>Cross-Media Fatherly</v>
       </c>
       <c r="G394" t="str">
-        <v>9410866</v>
+        <v>3633685</v>
       </c>
       <c r="H394" t="str">
-        <v>ZD142950</v>
+        <v/>
       </c>
       <c r="I394" t="str">
-        <v>2021-10-03T11:09:40.153Z</v>
+        <v>2021-05-28T07:54:08.679Z</v>
       </c>
       <c r="J394" t="str">
-        <v>10/3/2021, 7:09:40 AM</v>
+        <v>5/28/2021, 3:54:08 AM</v>
       </c>
       <c r="K394" t="str">
-        <v>2021-10-03T15:09:40.153Z</v>
+        <v>2021-05-28T09:54:08.679Z</v>
       </c>
       <c r="L394" t="str">
-        <v>10/3/2021, 11:09:40 AM</v>
+        <v>5/28/2021, 5:54:08 AM</v>
       </c>
       <c r="M394" t="str">
         <v>Calendar</v>
@@ -24825,57 +24824,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P394" t="str">
-        <v>2021-10-03T11:09:40.153Z</v>
+        <v>2021-05-28T07:54:08.679Z</v>
       </c>
       <c r="Q394" t="str">
-        <v>10/3/2021, 7:09:40 AM</v>
+        <v>5/28/2021, 3:54:08 AM</v>
       </c>
       <c r="R394" t="str">
-        <v>2021-10-03T13:49:40.153Z</v>
+        <v>2021-05-28T08:28:08.679Z</v>
       </c>
       <c r="S394" t="str">
-        <v>10/3/2021, 9:49:40 AM</v>
+        <v>5/28/2021, 4:28:08 AM</v>
       </c>
       <c r="T394">
-        <v>160</v>
+        <v>34</v>
       </c>
     </row>
     <row r="395">
       <c r="A395">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B395" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C395" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D395" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E395" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F395" t="str">
-        <v>Best-Of-Breed Firm Muddy</v>
+        <v>Frictionless Parched</v>
       </c>
       <c r="G395" t="str">
-        <v>9021727</v>
+        <v>1744024</v>
       </c>
       <c r="H395" t="str">
-        <v>ZD954701</v>
+        <v/>
       </c>
       <c r="I395" t="str">
-        <v>2021-10-04T20:52:38.319Z</v>
+        <v>2021-11-22T08:12:07.299Z</v>
       </c>
       <c r="J395" t="str">
-        <v>10/4/2021, 4:52:38 PM</v>
+        <v>11/22/2021, 3:12:07 AM</v>
       </c>
       <c r="K395" t="str">
-        <v>2021-10-04T23:52:38.319Z</v>
+        <v>2021-11-22T09:12:07.299Z</v>
       </c>
       <c r="L395" t="str">
-        <v>10/4/2021, 7:52:38 PM</v>
+        <v>11/22/2021, 4:12:07 AM</v>
       </c>
       <c r="M395" t="str">
         <v>Calendar</v>
@@ -24887,57 +24886,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P395" t="str">
-        <v>2021-10-04T20:52:38.319Z</v>
+        <v>2021-11-22T08:12:07.299Z</v>
       </c>
       <c r="Q395" t="str">
-        <v>10/4/2021, 4:52:38 PM</v>
+        <v>11/22/2021, 3:12:07 AM</v>
       </c>
       <c r="R395" t="str">
-        <v>2021-10-04T23:30:38.319Z</v>
+        <v>2021-11-22T09:06:07.299Z</v>
       </c>
       <c r="S395" t="str">
-        <v>10/4/2021, 7:30:38 PM</v>
+        <v>11/22/2021, 4:06:07 AM</v>
       </c>
       <c r="T395">
-        <v>158</v>
+        <v>54</v>
       </c>
     </row>
     <row r="396">
       <c r="A396">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B396" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C396" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D396" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E396" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F396" t="str">
-        <v>Magnetic Jubilantly Concrete Past</v>
+        <v>Impactful Instead Loosely</v>
       </c>
       <c r="G396" t="str">
-        <v>7639277</v>
+        <v>3585511</v>
       </c>
       <c r="H396" t="str">
         <v/>
       </c>
       <c r="I396" t="str">
-        <v>2021-12-25T23:06:28.007Z</v>
+        <v>2021-12-24T20:56:26.603Z</v>
       </c>
       <c r="J396" t="str">
-        <v>12/25/2021, 6:06:28 PM</v>
+        <v>12/24/2021, 3:56:26 PM</v>
       </c>
       <c r="K396" t="str">
-        <v>2021-12-26T01:06:28.007Z</v>
+        <v>2021-12-24T23:56:26.603Z</v>
       </c>
       <c r="L396" t="str">
-        <v>12/25/2021, 8:06:28 PM</v>
+        <v>12/24/2021, 6:56:26 PM</v>
       </c>
       <c r="M396" t="str">
         <v>Calendar</v>
@@ -24949,57 +24948,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P396" t="str">
-        <v>2021-12-25T23:06:28.007Z</v>
+        <v>2021-12-24T20:56:26.603Z</v>
       </c>
       <c r="Q396" t="str">
-        <v>12/25/2021, 6:06:28 PM</v>
+        <v>12/24/2021, 3:56:26 PM</v>
       </c>
       <c r="R396" t="str">
-        <v>2021-12-26T00:32:28.007Z</v>
+        <v>2021-12-24T22:38:26.603Z</v>
       </c>
       <c r="S396" t="str">
-        <v>12/25/2021, 7:32:28 PM</v>
+        <v>12/24/2021, 5:38:26 PM</v>
       </c>
       <c r="T396">
-        <v>86</v>
+        <v>102</v>
       </c>
     </row>
     <row r="397">
       <c r="A397">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B397" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C397" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D397" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E397" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F397" t="str">
-        <v>B2C Cuddly Refer Sin</v>
+        <v>Real-Time Provided Whose</v>
       </c>
       <c r="G397" t="str">
-        <v>4332519</v>
+        <v>5168421</v>
       </c>
       <c r="H397" t="str">
-        <v/>
+        <v>ZD085876</v>
       </c>
       <c r="I397" t="str">
-        <v>2021-12-29T01:05:31.852Z</v>
+        <v>2021-12-28T11:39:48.505Z</v>
       </c>
       <c r="J397" t="str">
-        <v>12/28/2021, 8:05:31 PM</v>
+        <v>12/28/2021, 6:39:48 AM</v>
       </c>
       <c r="K397" t="str">
-        <v>2021-12-29T03:05:31.852Z</v>
+        <v>2021-12-28T15:39:48.505Z</v>
       </c>
       <c r="L397" t="str">
-        <v>12/28/2021, 10:05:31 PM</v>
+        <v>12/28/2021, 10:39:48 AM</v>
       </c>
       <c r="M397" t="str">
         <v>Calendar</v>
@@ -25011,57 +25010,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P397" t="str">
-        <v>2021-12-29T01:05:31.852Z</v>
+        <v>2021-12-28T11:39:48.505Z</v>
       </c>
       <c r="Q397" t="str">
-        <v>12/28/2021, 8:05:31 PM</v>
+        <v>12/28/2021, 6:39:48 AM</v>
       </c>
       <c r="R397" t="str">
-        <v>2021-12-29T02:44:31.852Z</v>
+        <v>2021-12-28T13:15:48.505Z</v>
       </c>
       <c r="S397" t="str">
-        <v>12/28/2021, 9:44:31 PM</v>
+        <v>12/28/2021, 8:15:48 AM</v>
       </c>
       <c r="T397">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="398">
       <c r="A398">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B398" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C398" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D398" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E398" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F398" t="str">
-        <v>Collaborative Provided Tightly Toe</v>
+        <v>End-To-End Optimistically</v>
       </c>
       <c r="G398" t="str">
-        <v>2481380</v>
+        <v>4170923</v>
       </c>
       <c r="H398" t="str">
-        <v>ZD623154</v>
+        <v/>
       </c>
       <c r="I398" t="str">
-        <v>2022-03-25T10:53:48.781Z</v>
+        <v>2022-02-20T05:23:33.522Z</v>
       </c>
       <c r="J398" t="str">
-        <v>3/25/2022, 6:53:48 AM</v>
+        <v>2/20/2022, 12:23:33 AM</v>
       </c>
       <c r="K398" t="str">
-        <v>2022-03-25T12:53:48.781Z</v>
+        <v>2022-02-20T09:23:33.522Z</v>
       </c>
       <c r="L398" t="str">
-        <v>3/25/2022, 8:53:48 AM</v>
+        <v>2/20/2022, 4:23:33 AM</v>
       </c>
       <c r="M398" t="str">
         <v>Calendar</v>
@@ -25073,57 +25072,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P398" t="str">
-        <v>2022-03-25T10:53:48.781Z</v>
+        <v>2022-02-20T05:23:33.522Z</v>
       </c>
       <c r="Q398" t="str">
-        <v>3/25/2022, 6:53:48 AM</v>
+        <v>2/20/2022, 12:23:33 AM</v>
       </c>
       <c r="R398" t="str">
-        <v>2022-03-25T12:36:48.781Z</v>
+        <v>2022-02-20T07:30:33.522Z</v>
       </c>
       <c r="S398" t="str">
-        <v>3/25/2022, 8:36:48 AM</v>
+        <v>2/20/2022, 2:30:33 AM</v>
       </c>
       <c r="T398">
-        <v>103</v>
+        <v>127</v>
       </c>
     </row>
     <row r="399">
       <c r="A399">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B399" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C399" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D399" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E399" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F399" t="str">
-        <v>Synergistic Fail</v>
+        <v>Open-Source Whoa Energetically</v>
       </c>
       <c r="G399" t="str">
-        <v>1165545</v>
+        <v>8201648</v>
       </c>
       <c r="H399" t="str">
-        <v>ZD858854</v>
+        <v/>
       </c>
       <c r="I399" t="str">
-        <v>2022-07-03T21:12:11.202Z</v>
+        <v>2022-05-10T04:32:28.755Z</v>
       </c>
       <c r="J399" t="str">
-        <v>7/3/2022, 5:12:11 PM</v>
+        <v>5/10/2022, 12:32:28 AM</v>
       </c>
       <c r="K399" t="str">
-        <v>2022-07-03T23:12:11.202Z</v>
+        <v>2022-05-10T06:32:28.755Z</v>
       </c>
       <c r="L399" t="str">
-        <v>7/3/2022, 7:12:11 PM</v>
+        <v>5/10/2022, 2:32:28 AM</v>
       </c>
       <c r="M399" t="str">
         <v>Calendar</v>
@@ -25135,57 +25134,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P399" t="str">
-        <v>2022-07-03T21:12:11.202Z</v>
+        <v>2022-05-10T04:32:28.755Z</v>
       </c>
       <c r="Q399" t="str">
-        <v>7/3/2022, 5:12:11 PM</v>
+        <v>5/10/2022, 12:32:28 AM</v>
       </c>
       <c r="R399" t="str">
-        <v>2022-07-03T21:53:11.202Z</v>
+        <v>2022-05-10T05:15:28.755Z</v>
       </c>
       <c r="S399" t="str">
-        <v>7/3/2022, 5:53:11 PM</v>
+        <v>5/10/2022, 1:15:28 AM</v>
       </c>
       <c r="T399">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="400">
       <c r="A400">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B400" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C400" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D400" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E400" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F400" t="str">
-        <v>Plug-And-Play Knight</v>
+        <v>Cutting-Edge Irk Disclosure Whereas</v>
       </c>
       <c r="G400" t="str">
-        <v>8655283</v>
+        <v>5917518</v>
       </c>
       <c r="H400" t="str">
-        <v>ZD239676</v>
+        <v/>
       </c>
       <c r="I400" t="str">
-        <v>2022-08-13T06:28:29.802Z</v>
+        <v>2022-05-23T10:12:17.488Z</v>
       </c>
       <c r="J400" t="str">
-        <v>8/13/2022, 2:28:29 AM</v>
+        <v>5/23/2022, 6:12:17 AM</v>
       </c>
       <c r="K400" t="str">
-        <v>2022-08-13T08:28:29.802Z</v>
+        <v>2022-05-23T14:12:17.488Z</v>
       </c>
       <c r="L400" t="str">
-        <v>8/13/2022, 4:28:29 AM</v>
+        <v>5/23/2022, 10:12:17 AM</v>
       </c>
       <c r="M400" t="str">
         <v>Calendar</v>
@@ -25197,57 +25196,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P400" t="str">
-        <v>2022-08-13T06:28:29.802Z</v>
+        <v>2022-05-23T10:12:17.488Z</v>
       </c>
       <c r="Q400" t="str">
-        <v>8/13/2022, 2:28:29 AM</v>
+        <v>5/23/2022, 6:12:17 AM</v>
       </c>
       <c r="R400" t="str">
-        <v>2022-08-13T07:27:29.802Z</v>
+        <v>2022-05-23T11:05:17.488Z</v>
       </c>
       <c r="S400" t="str">
-        <v>8/13/2022, 3:27:29 AM</v>
+        <v>5/23/2022, 7:05:17 AM</v>
       </c>
       <c r="T400">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="401">
       <c r="A401">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B401" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C401" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D401" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E401" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F401" t="str">
-        <v>Open-Source Whoa Scare</v>
+        <v>Decentralized Maroon Yowza Like</v>
       </c>
       <c r="G401" t="str">
-        <v>4800039</v>
+        <v>3783409</v>
       </c>
       <c r="H401" t="str">
         <v/>
       </c>
       <c r="I401" t="str">
-        <v>2022-10-17T03:51:22.824Z</v>
+        <v>2022-08-29T04:44:07.275Z</v>
       </c>
       <c r="J401" t="str">
-        <v>10/16/2022, 11:51:22 PM</v>
+        <v>8/29/2022, 12:44:07 AM</v>
       </c>
       <c r="K401" t="str">
-        <v>2022-10-17T04:51:22.824Z</v>
+        <v>2022-08-29T05:44:07.275Z</v>
       </c>
       <c r="L401" t="str">
-        <v>10/17/2022, 12:51:22 AM</v>
+        <v>8/29/2022, 1:44:07 AM</v>
       </c>
       <c r="M401" t="str">
         <v>Calendar</v>
@@ -25259,57 +25258,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P401" t="str">
-        <v>2022-10-17T03:51:22.824Z</v>
+        <v>2022-08-29T04:44:07.275Z</v>
       </c>
       <c r="Q401" t="str">
-        <v>10/16/2022, 11:51:22 PM</v>
+        <v>8/29/2022, 12:44:07 AM</v>
       </c>
       <c r="R401" t="str">
-        <v>2022-10-17T04:31:22.824Z</v>
+        <v>2022-08-29T05:32:07.275Z</v>
       </c>
       <c r="S401" t="str">
-        <v>10/17/2022, 12:31:22 AM</v>
+        <v>8/29/2022, 1:32:07 AM</v>
       </c>
       <c r="T401">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="402">
       <c r="A402">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B402" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C402" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D402" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E402" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F402" t="str">
-        <v>Proactive Although</v>
+        <v>Bleeding-Edge Hunger Near Recent</v>
       </c>
       <c r="G402" t="str">
-        <v>3017429</v>
+        <v>6998574</v>
       </c>
       <c r="H402" t="str">
-        <v/>
+        <v>ZD697010</v>
       </c>
       <c r="I402" t="str">
-        <v>2022-12-18T14:34:20.684Z</v>
+        <v>2022-12-07T18:35:11.058Z</v>
       </c>
       <c r="J402" t="str">
-        <v>12/18/2022, 9:34:20 AM</v>
+        <v>12/7/2022, 1:35:11 PM</v>
       </c>
       <c r="K402" t="str">
-        <v>2022-12-18T17:34:20.684Z</v>
+        <v>2022-12-07T22:35:11.058Z</v>
       </c>
       <c r="L402" t="str">
-        <v>12/18/2022, 12:34:20 PM</v>
+        <v>12/7/2022, 5:35:11 PM</v>
       </c>
       <c r="M402" t="str">
         <v>Calendar</v>
@@ -25321,57 +25320,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P402" t="str">
-        <v>2022-12-18T14:34:20.684Z</v>
+        <v>2022-12-07T18:35:11.058Z</v>
       </c>
       <c r="Q402" t="str">
-        <v>12/18/2022, 9:34:20 AM</v>
+        <v>12/7/2022, 1:35:11 PM</v>
       </c>
       <c r="R402" t="str">
-        <v>2022-12-18T15:44:20.684Z</v>
+        <v>2022-12-07T20:50:11.058Z</v>
       </c>
       <c r="S402" t="str">
-        <v>12/18/2022, 10:44:20 AM</v>
+        <v>12/7/2022, 3:50:11 PM</v>
       </c>
       <c r="T402">
-        <v>70</v>
+        <v>135</v>
       </c>
     </row>
     <row r="403">
       <c r="A403">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="B403" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C403" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D403" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E403" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F403" t="str">
-        <v>Best-Of-Breed Between Manner</v>
+        <v>Strategic Psst</v>
       </c>
       <c r="G403" t="str">
-        <v>7618409</v>
+        <v>6544455</v>
       </c>
       <c r="H403" t="str">
-        <v/>
+        <v>ZD928373</v>
       </c>
       <c r="I403" t="str">
-        <v>2023-03-01T01:53:42.807Z</v>
+        <v>2022-12-17T14:57:48.978Z</v>
       </c>
       <c r="J403" t="str">
-        <v>2/28/2023, 8:53:42 PM</v>
+        <v>12/17/2022, 9:57:48 AM</v>
       </c>
       <c r="K403" t="str">
-        <v>2023-03-01T02:53:42.807Z</v>
+        <v>2022-12-17T17:57:48.978Z</v>
       </c>
       <c r="L403" t="str">
-        <v>2/28/2023, 9:53:42 PM</v>
+        <v>12/17/2022, 12:57:48 PM</v>
       </c>
       <c r="M403" t="str">
         <v>Calendar</v>
@@ -25383,57 +25382,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P403" t="str">
-        <v>2023-03-01T01:53:42.807Z</v>
+        <v>2022-12-17T14:57:48.978Z</v>
       </c>
       <c r="Q403" t="str">
-        <v>2/28/2023, 8:53:42 PM</v>
+        <v>12/17/2022, 9:57:48 AM</v>
       </c>
       <c r="R403" t="str">
-        <v>2023-03-01T02:24:42.807Z</v>
+        <v>2022-12-17T17:05:48.978Z</v>
       </c>
       <c r="S403" t="str">
-        <v>2/28/2023, 9:24:42 PM</v>
+        <v>12/17/2022, 12:05:48 PM</v>
       </c>
       <c r="T403">
-        <v>31</v>
+        <v>128</v>
       </c>
     </row>
     <row r="404">
       <c r="A404">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="B404" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C404" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D404" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E404" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F404" t="str">
-        <v>Best-Of-Breed Bestride Than</v>
+        <v>Efficient Warped Rapidly</v>
       </c>
       <c r="G404" t="str">
-        <v>1357785</v>
+        <v>1081949</v>
       </c>
       <c r="H404" t="str">
-        <v>ZD858960</v>
+        <v/>
       </c>
       <c r="I404" t="str">
-        <v>2023-07-31T02:37:43.247Z</v>
+        <v>2023-01-07T04:35:36.436Z</v>
       </c>
       <c r="J404" t="str">
-        <v>7/30/2023, 10:37:43 PM</v>
+        <v>1/6/2023, 11:35:36 PM</v>
       </c>
       <c r="K404" t="str">
-        <v>2023-07-31T05:37:43.247Z</v>
+        <v>2023-01-07T07:35:36.436Z</v>
       </c>
       <c r="L404" t="str">
-        <v>7/31/2023, 1:37:43 AM</v>
+        <v>1/7/2023, 2:35:36 AM</v>
       </c>
       <c r="M404" t="str">
         <v>Calendar</v>
@@ -25445,57 +25444,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P404" t="str">
-        <v>2023-07-31T02:37:43.247Z</v>
+        <v>2023-01-07T04:35:36.436Z</v>
       </c>
       <c r="Q404" t="str">
-        <v>7/30/2023, 10:37:43 PM</v>
+        <v>1/6/2023, 11:35:36 PM</v>
       </c>
       <c r="R404" t="str">
-        <v>2023-07-31T05:33:43.247Z</v>
+        <v>2023-01-07T05:42:36.436Z</v>
       </c>
       <c r="S404" t="str">
-        <v>7/31/2023, 1:33:43 AM</v>
+        <v>1/7/2023, 12:42:36 AM</v>
       </c>
       <c r="T404">
-        <v>176</v>
+        <v>67</v>
       </c>
     </row>
     <row r="405">
       <c r="A405">
-        <v>338</v>
+        <v>272</v>
       </c>
       <c r="B405" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C405" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D405" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E405" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F405" t="str">
-        <v>Customized Jittery</v>
+        <v>B2B Frankly Ring Fooey</v>
       </c>
       <c r="G405" t="str">
-        <v>2986821</v>
+        <v>7901231</v>
       </c>
       <c r="H405" t="str">
-        <v/>
+        <v>ZD446960</v>
       </c>
       <c r="I405" t="str">
-        <v>2024-04-07T13:56:58.000Z</v>
+        <v>2023-03-11T01:27:40.998Z</v>
       </c>
       <c r="J405" t="str">
-        <v>4/7/2024, 9:56:58 AM</v>
+        <v>3/10/2023, 8:27:40 PM</v>
       </c>
       <c r="K405" t="str">
-        <v>2024-04-07T14:56:58.000Z</v>
+        <v>2023-03-11T02:27:40.998Z</v>
       </c>
       <c r="L405" t="str">
-        <v>4/7/2024, 10:56:58 AM</v>
+        <v>3/10/2023, 9:27:40 PM</v>
       </c>
       <c r="M405" t="str">
         <v>Calendar</v>
@@ -25507,57 +25506,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P405" t="str">
-        <v>2024-04-07T13:56:58.000Z</v>
+        <v>2023-03-11T01:27:40.998Z</v>
       </c>
       <c r="Q405" t="str">
-        <v>4/7/2024, 9:56:58 AM</v>
+        <v>3/10/2023, 8:27:40 PM</v>
       </c>
       <c r="R405" t="str">
-        <v>2024-04-07T14:53:58.000Z</v>
+        <v>2023-03-11T02:01:40.998Z</v>
       </c>
       <c r="S405" t="str">
-        <v>4/7/2024, 10:53:58 AM</v>
+        <v>3/10/2023, 9:01:40 PM</v>
       </c>
       <c r="T405">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="406">
       <c r="A406">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="B406" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C406" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D406" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E406" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F406" t="str">
-        <v>Interactive Towards Scary Spark</v>
+        <v>B2B However</v>
       </c>
       <c r="G406" t="str">
-        <v>9580649</v>
+        <v>9852289</v>
       </c>
       <c r="H406" t="str">
-        <v>ZD605972</v>
+        <v>ZD123540</v>
       </c>
       <c r="I406" t="str">
-        <v>2024-04-19T23:56:39.254Z</v>
+        <v>2023-04-14T02:13:30.363Z</v>
       </c>
       <c r="J406" t="str">
-        <v>4/19/2024, 7:56:39 PM</v>
+        <v>4/13/2023, 10:13:30 PM</v>
       </c>
       <c r="K406" t="str">
-        <v>2024-04-20T02:56:39.254Z</v>
+        <v>2023-04-14T03:13:30.363Z</v>
       </c>
       <c r="L406" t="str">
-        <v>4/19/2024, 10:56:39 PM</v>
+        <v>4/13/2023, 11:13:30 PM</v>
       </c>
       <c r="M406" t="str">
         <v>Calendar</v>
@@ -25569,57 +25568,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P406" t="str">
-        <v>2024-04-19T23:56:39.254Z</v>
+        <v>2023-04-14T02:13:30.363Z</v>
       </c>
       <c r="Q406" t="str">
-        <v>4/19/2024, 7:56:39 PM</v>
+        <v>4/13/2023, 10:13:30 PM</v>
       </c>
       <c r="R406" t="str">
-        <v>2024-04-20T01:47:39.254Z</v>
+        <v>2023-04-14T03:09:30.363Z</v>
       </c>
       <c r="S406" t="str">
-        <v>4/19/2024, 9:47:39 PM</v>
+        <v>4/13/2023, 11:09:30 PM</v>
       </c>
       <c r="T406">
-        <v>111</v>
+        <v>56</v>
       </c>
     </row>
     <row r="407">
       <c r="A407">
-        <v>342</v>
+        <v>285</v>
       </c>
       <c r="B407" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C407" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D407" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E407" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F407" t="str">
-        <v>Leading-Edge Instead Onto</v>
+        <v>Integrated Whether Whose Supposing</v>
       </c>
       <c r="G407" t="str">
-        <v>8219162</v>
+        <v>4738095</v>
       </c>
       <c r="H407" t="str">
-        <v/>
+        <v>ZD591142</v>
       </c>
       <c r="I407" t="str">
-        <v>2024-04-20T20:35:33.201Z</v>
+        <v>2023-06-03T20:11:54.133Z</v>
       </c>
       <c r="J407" t="str">
-        <v>4/20/2024, 4:35:33 PM</v>
+        <v>6/3/2023, 4:11:54 PM</v>
       </c>
       <c r="K407" t="str">
-        <v>2024-04-21T00:35:33.201Z</v>
+        <v>2023-06-03T23:11:54.133Z</v>
       </c>
       <c r="L407" t="str">
-        <v>4/20/2024, 8:35:33 PM</v>
+        <v>6/3/2023, 7:11:54 PM</v>
       </c>
       <c r="M407" t="str">
         <v>Calendar</v>
@@ -25631,57 +25630,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P407" t="str">
-        <v>2024-04-20T20:35:33.201Z</v>
+        <v>2023-06-03T20:11:54.133Z</v>
       </c>
       <c r="Q407" t="str">
-        <v>4/20/2024, 4:35:33 PM</v>
+        <v>6/3/2023, 4:11:54 PM</v>
       </c>
       <c r="R407" t="str">
-        <v>2024-04-20T23:49:33.201Z</v>
+        <v>2023-06-03T21:03:54.133Z</v>
       </c>
       <c r="S407" t="str">
-        <v>4/20/2024, 7:49:33 PM</v>
+        <v>6/3/2023, 5:03:54 PM</v>
       </c>
       <c r="T407">
-        <v>194</v>
+        <v>52</v>
       </c>
     </row>
     <row r="408">
       <c r="A408">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="B408" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C408" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D408" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E408" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F408" t="str">
-        <v>User-Centric Upon Quick</v>
+        <v>Sustainable Unimpressively Quaintly</v>
       </c>
       <c r="G408" t="str">
-        <v>3358770</v>
+        <v>7532000</v>
       </c>
       <c r="H408" t="str">
-        <v>ZD706372</v>
+        <v/>
       </c>
       <c r="I408" t="str">
-        <v>2024-07-03T19:05:35.333Z</v>
+        <v>2023-08-10T15:11:28.172Z</v>
       </c>
       <c r="J408" t="str">
-        <v>7/3/2024, 3:05:35 PM</v>
+        <v>8/10/2023, 11:11:28 AM</v>
       </c>
       <c r="K408" t="str">
-        <v>2024-07-03T23:05:35.333Z</v>
+        <v>2023-08-10T16:11:28.172Z</v>
       </c>
       <c r="L408" t="str">
-        <v>7/3/2024, 7:05:35 PM</v>
+        <v>8/10/2023, 12:11:28 PM</v>
       </c>
       <c r="M408" t="str">
         <v>Calendar</v>
@@ -25693,57 +25692,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P408" t="str">
-        <v>2024-07-03T19:05:35.333Z</v>
+        <v>2023-08-10T15:11:28.172Z</v>
       </c>
       <c r="Q408" t="str">
-        <v>7/3/2024, 3:05:35 PM</v>
+        <v>8/10/2023, 11:11:28 AM</v>
       </c>
       <c r="R408" t="str">
-        <v>2024-07-03T20:56:35.333Z</v>
+        <v>2023-08-10T15:46:28.172Z</v>
       </c>
       <c r="S408" t="str">
-        <v>7/3/2024, 4:56:35 PM</v>
+        <v>8/10/2023, 11:46:28 AM</v>
       </c>
       <c r="T408">
-        <v>111</v>
+        <v>35</v>
       </c>
     </row>
     <row r="409">
       <c r="A409">
-        <v>380</v>
+        <v>294</v>
       </c>
       <c r="B409" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C409" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D409" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E409" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F409" t="str">
-        <v>AI-Driven Over Loftily</v>
+        <v>World-Class Ha Gee Corporation</v>
       </c>
       <c r="G409" t="str">
-        <v>3052879</v>
+        <v>4666356</v>
       </c>
       <c r="H409" t="str">
-        <v>ZD408733</v>
+        <v/>
       </c>
       <c r="I409" t="str">
-        <v>2024-12-19T10:49:24.776Z</v>
+        <v>2023-08-14T13:45:04.550Z</v>
       </c>
       <c r="J409" t="str">
-        <v>12/19/2024, 5:49:24 AM</v>
+        <v>8/14/2023, 9:45:04 AM</v>
       </c>
       <c r="K409" t="str">
-        <v>2024-12-19T11:49:24.776Z</v>
+        <v>2023-08-14T15:45:04.550Z</v>
       </c>
       <c r="L409" t="str">
-        <v>12/19/2024, 6:49:24 AM</v>
+        <v>8/14/2023, 11:45:04 AM</v>
       </c>
       <c r="M409" t="str">
         <v>Calendar</v>
@@ -25755,57 +25754,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P409" t="str">
-        <v>2024-12-19T10:49:24.776Z</v>
+        <v>2023-08-14T13:45:04.550Z</v>
       </c>
       <c r="Q409" t="str">
-        <v>12/19/2024, 5:49:24 AM</v>
+        <v>8/14/2023, 9:45:04 AM</v>
       </c>
       <c r="R409" t="str">
-        <v>2024-12-19T11:38:24.776Z</v>
+        <v>2023-08-14T15:16:04.550Z</v>
       </c>
       <c r="S409" t="str">
-        <v>12/19/2024, 6:38:24 AM</v>
+        <v>8/14/2023, 11:16:04 AM</v>
       </c>
       <c r="T409">
-        <v>49</v>
+        <v>91</v>
       </c>
     </row>
     <row r="410">
       <c r="A410">
-        <v>382</v>
+        <v>295</v>
       </c>
       <c r="B410" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C410" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D410" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E410" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F410" t="str">
-        <v>Real-Time Mostly Little</v>
+        <v>Proactive Promptly</v>
       </c>
       <c r="G410" t="str">
-        <v>4768999</v>
+        <v>4791935</v>
       </c>
       <c r="H410" t="str">
-        <v/>
+        <v>ZD538519</v>
       </c>
       <c r="I410" t="str">
-        <v>2025-01-12T12:41:34.835Z</v>
+        <v>2023-08-21T23:30:42.618Z</v>
       </c>
       <c r="J410" t="str">
-        <v>1/12/2025, 7:41:34 AM</v>
+        <v>8/21/2023, 7:30:42 PM</v>
       </c>
       <c r="K410" t="str">
-        <v>2025-01-12T14:41:34.835Z</v>
+        <v>2023-08-22T00:30:42.618Z</v>
       </c>
       <c r="L410" t="str">
-        <v>1/12/2025, 9:41:34 AM</v>
+        <v>8/21/2023, 8:30:42 PM</v>
       </c>
       <c r="M410" t="str">
         <v>Calendar</v>
@@ -25817,57 +25816,57 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P410" t="str">
-        <v>2025-01-12T12:41:34.835Z</v>
+        <v>2023-08-21T23:30:42.618Z</v>
       </c>
       <c r="Q410" t="str">
-        <v>1/12/2025, 7:41:34 AM</v>
+        <v>8/21/2023, 7:30:42 PM</v>
       </c>
       <c r="R410" t="str">
-        <v>2025-01-12T14:10:34.835Z</v>
+        <v>2023-08-22T00:23:42.618Z</v>
       </c>
       <c r="S410" t="str">
-        <v>1/12/2025, 9:10:34 AM</v>
+        <v>8/21/2023, 8:23:42 PM</v>
       </c>
       <c r="T410">
-        <v>89</v>
+        <v>53</v>
       </c>
     </row>
     <row r="411">
       <c r="A411">
-        <v>442</v>
+        <v>306</v>
       </c>
       <c r="B411" t="str">
-        <v>Morgan Johnson</v>
+        <v>Nicholas Villiers</v>
       </c>
       <c r="C411" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="D411" t="str">
-        <v>admin-morganjohnson-2@fgcu.local</v>
+        <v>nickvboy@gmail.com</v>
       </c>
       <c r="E411" t="str">
-        <v>6607887497</v>
+        <v>2096922639</v>
       </c>
       <c r="F411" t="str">
-        <v>Compelling Wavy</v>
+        <v>Mission-Critical Gracefully</v>
       </c>
       <c r="G411" t="str">
-        <v>9233048</v>
+        <v>3941293</v>
       </c>
       <c r="H411" t="str">
-        <v>ZD717770</v>
+        <v/>
       </c>
       <c r="I411" t="str">
-        <v>2025-12-05T15:45:24.288Z</v>
+        <v>2023-10-18T08:16:14.947Z</v>
       </c>
       <c r="J411" t="str">
-        <v>12/5/2025, 10:45:24 AM</v>
+        <v>10/18/2023, 4:16:14 AM</v>
       </c>
       <c r="K411" t="str">
-        <v>2025-12-05T19:45:24.288Z</v>
+        <v>2023-10-18T11:16:14.947Z</v>
       </c>
       <c r="L411" t="str">
-        <v>12/5/2025, 2:45:24 PM</v>
+        <v>10/18/2023, 7:16:14 AM</v>
       </c>
       <c r="M411" t="str">
         <v>Calendar</v>
@@ -25879,24 +25878,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P411" t="str">
-        <v>2025-12-05T15:45:24.288Z</v>
+        <v>2023-10-18T08:16:14.947Z</v>
       </c>
       <c r="Q411" t="str">
-        <v>12/5/2025, 10:45:24 AM</v>
+        <v>10/18/2023, 4:16:14 AM</v>
       </c>
       <c r="R411" t="str">
-        <v>2025-12-05T16:43:24.288Z</v>
+        <v>2023-10-18T10:07:14.947Z</v>
       </c>
       <c r="S411" t="str">
-        <v>12/5/2025, 11:43:24 AM</v>
+        <v>10/18/2023, 6:07:14 AM</v>
       </c>
       <c r="T411">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="412">
       <c r="A412">
-        <v>38</v>
+        <v>311</v>
       </c>
       <c r="B412" t="str">
         <v>Nicholas Villiers</v>
@@ -25911,25 +25910,25 @@
         <v>2096922639</v>
       </c>
       <c r="F412" t="str">
-        <v>Frictionless Since</v>
+        <v>Quantum Deform</v>
       </c>
       <c r="G412" t="str">
-        <v>6252695</v>
+        <v>1390667</v>
       </c>
       <c r="H412" t="str">
-        <v/>
+        <v>ZD439444</v>
       </c>
       <c r="I412" t="str">
-        <v>2019-09-19T23:26:13.453Z</v>
+        <v>2023-11-11T00:58:17.243Z</v>
       </c>
       <c r="J412" t="str">
-        <v>9/19/2019, 7:26:13 PM</v>
+        <v>11/10/2023, 7:58:17 PM</v>
       </c>
       <c r="K412" t="str">
-        <v>2019-09-20T03:26:13.453Z</v>
+        <v>2023-11-11T04:58:17.243Z</v>
       </c>
       <c r="L412" t="str">
-        <v>9/19/2019, 11:26:13 PM</v>
+        <v>11/10/2023, 11:58:17 PM</v>
       </c>
       <c r="M412" t="str">
         <v>Calendar</v>
@@ -25941,24 +25940,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P412" t="str">
-        <v>2019-09-19T23:26:13.453Z</v>
+        <v>2023-11-11T00:58:17.243Z</v>
       </c>
       <c r="Q412" t="str">
-        <v>9/19/2019, 7:26:13 PM</v>
+        <v>11/10/2023, 7:58:17 PM</v>
       </c>
       <c r="R412" t="str">
-        <v>2019-09-20T02:56:13.453Z</v>
+        <v>2023-11-11T04:58:17.243Z</v>
       </c>
       <c r="S412" t="str">
-        <v>9/19/2019, 10:56:13 PM</v>
+        <v>11/10/2023, 11:58:17 PM</v>
       </c>
       <c r="T412">
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
     <row r="413">
       <c r="A413">
-        <v>41</v>
+        <v>314</v>
       </c>
       <c r="B413" t="str">
         <v>Nicholas Villiers</v>
@@ -25973,25 +25972,25 @@
         <v>2096922639</v>
       </c>
       <c r="F413" t="str">
-        <v>Customized Very Painfully Furthermore</v>
+        <v>Immersive Hopeful</v>
       </c>
       <c r="G413" t="str">
-        <v>5149801</v>
+        <v>1113264</v>
       </c>
       <c r="H413" t="str">
-        <v>ZD673155</v>
+        <v/>
       </c>
       <c r="I413" t="str">
-        <v>2019-09-28T03:05:58.091Z</v>
+        <v>2023-12-01T15:08:43.402Z</v>
       </c>
       <c r="J413" t="str">
-        <v>9/27/2019, 11:05:58 PM</v>
+        <v>12/1/2023, 10:08:43 AM</v>
       </c>
       <c r="K413" t="str">
-        <v>2019-09-28T07:05:58.091Z</v>
+        <v>2023-12-01T16:08:43.402Z</v>
       </c>
       <c r="L413" t="str">
-        <v>9/28/2019, 3:05:58 AM</v>
+        <v>12/1/2023, 11:08:43 AM</v>
       </c>
       <c r="M413" t="str">
         <v>Calendar</v>
@@ -26003,24 +26002,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P413" t="str">
-        <v>2019-09-28T03:05:58.091Z</v>
+        <v>2023-12-01T15:08:43.402Z</v>
       </c>
       <c r="Q413" t="str">
-        <v>9/27/2019, 11:05:58 PM</v>
+        <v>12/1/2023, 10:08:43 AM</v>
       </c>
       <c r="R413" t="str">
-        <v>2019-09-28T03:46:58.091Z</v>
+        <v>2023-12-01T16:04:43.402Z</v>
       </c>
       <c r="S413" t="str">
-        <v>9/27/2019, 11:46:58 PM</v>
+        <v>12/1/2023, 11:04:43 AM</v>
       </c>
       <c r="T413">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="414">
       <c r="A414">
-        <v>46</v>
+        <v>343</v>
       </c>
       <c r="B414" t="str">
         <v>Nicholas Villiers</v>
@@ -26035,25 +26034,25 @@
         <v>2096922639</v>
       </c>
       <c r="F414" t="str">
-        <v>Customized Enthusiastically Aw</v>
+        <v>B2B Poorly Good When</v>
       </c>
       <c r="G414" t="str">
-        <v>5957300</v>
+        <v>1241383</v>
       </c>
       <c r="H414" t="str">
-        <v/>
+        <v>ZD533094</v>
       </c>
       <c r="I414" t="str">
-        <v>2019-10-14T11:41:20.403Z</v>
+        <v>2024-05-14T01:17:12.088Z</v>
       </c>
       <c r="J414" t="str">
-        <v>10/14/2019, 7:41:20 AM</v>
+        <v>5/13/2024, 9:17:12 PM</v>
       </c>
       <c r="K414" t="str">
-        <v>2019-10-14T13:41:20.403Z</v>
+        <v>2024-05-14T02:17:12.088Z</v>
       </c>
       <c r="L414" t="str">
-        <v>10/14/2019, 9:41:20 AM</v>
+        <v>5/13/2024, 10:17:12 PM</v>
       </c>
       <c r="M414" t="str">
         <v>Calendar</v>
@@ -26065,24 +26064,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P414" t="str">
-        <v>2019-10-14T11:41:20.403Z</v>
+        <v>2024-05-14T01:17:12.088Z</v>
       </c>
       <c r="Q414" t="str">
-        <v>10/14/2019, 7:41:20 AM</v>
+        <v>5/13/2024, 9:17:12 PM</v>
       </c>
       <c r="R414" t="str">
-        <v>2019-10-14T13:41:20.403Z</v>
+        <v>2024-05-14T01:55:12.088Z</v>
       </c>
       <c r="S414" t="str">
-        <v>10/14/2019, 9:41:20 AM</v>
+        <v>5/13/2024, 9:55:12 PM</v>
       </c>
       <c r="T414">
-        <v>120</v>
+        <v>38</v>
       </c>
     </row>
     <row r="415">
       <c r="A415">
-        <v>58</v>
+        <v>355</v>
       </c>
       <c r="B415" t="str">
         <v>Nicholas Villiers</v>
@@ -26097,25 +26096,25 @@
         <v>2096922639</v>
       </c>
       <c r="F415" t="str">
-        <v>One-To-One Verify Eek</v>
+        <v>Sustainable Per Disrespect</v>
       </c>
       <c r="G415" t="str">
-        <v>6433652</v>
+        <v>1054197</v>
       </c>
       <c r="H415" t="str">
-        <v>ZD386532</v>
+        <v>ZD813098</v>
       </c>
       <c r="I415" t="str">
-        <v>2019-12-06T11:32:21.401Z</v>
+        <v>2024-06-27T09:57:01.223Z</v>
       </c>
       <c r="J415" t="str">
-        <v>12/6/2019, 6:32:21 AM</v>
+        <v>6/27/2024, 5:57:01 AM</v>
       </c>
       <c r="K415" t="str">
-        <v>2019-12-06T13:32:21.401Z</v>
+        <v>2024-06-27T13:57:01.223Z</v>
       </c>
       <c r="L415" t="str">
-        <v>12/6/2019, 8:32:21 AM</v>
+        <v>6/27/2024, 9:57:01 AM</v>
       </c>
       <c r="M415" t="str">
         <v>Calendar</v>
@@ -26127,24 +26126,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P415" t="str">
-        <v>2019-12-06T11:32:21.401Z</v>
+        <v>2024-06-27T09:57:01.223Z</v>
       </c>
       <c r="Q415" t="str">
-        <v>12/6/2019, 6:32:21 AM</v>
+        <v>6/27/2024, 5:57:01 AM</v>
       </c>
       <c r="R415" t="str">
-        <v>2019-12-06T12:14:21.401Z</v>
+        <v>2024-06-27T11:17:01.223Z</v>
       </c>
       <c r="S415" t="str">
-        <v>12/6/2019, 7:14:21 AM</v>
+        <v>6/27/2024, 7:17:01 AM</v>
       </c>
       <c r="T415">
-        <v>42</v>
+        <v>80</v>
       </c>
     </row>
     <row r="416">
       <c r="A416">
-        <v>76</v>
+        <v>381</v>
       </c>
       <c r="B416" t="str">
         <v>Nicholas Villiers</v>
@@ -26159,25 +26158,25 @@
         <v>2096922639</v>
       </c>
       <c r="F416" t="str">
-        <v>Bleeding-Edge Incidentally Secondary</v>
+        <v>Collaborative Noted Er Boo</v>
       </c>
       <c r="G416" t="str">
-        <v>7350535</v>
+        <v>4990954</v>
       </c>
       <c r="H416" t="str">
-        <v/>
+        <v>ZD895021</v>
       </c>
       <c r="I416" t="str">
-        <v>2020-03-26T03:42:03.701Z</v>
+        <v>2024-12-25T02:33:26.902Z</v>
       </c>
       <c r="J416" t="str">
-        <v>3/25/2020, 11:42:03 PM</v>
+        <v>12/24/2024, 9:33:26 PM</v>
       </c>
       <c r="K416" t="str">
-        <v>2020-03-26T07:42:03.701Z</v>
+        <v>2024-12-25T05:33:26.902Z</v>
       </c>
       <c r="L416" t="str">
-        <v>3/26/2020, 3:42:03 AM</v>
+        <v>12/25/2024, 12:33:26 AM</v>
       </c>
       <c r="M416" t="str">
         <v>Calendar</v>
@@ -26189,24 +26188,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P416" t="str">
-        <v>2020-03-26T03:42:03.701Z</v>
+        <v>2024-12-25T02:33:26.902Z</v>
       </c>
       <c r="Q416" t="str">
-        <v>3/25/2020, 11:42:03 PM</v>
+        <v>12/24/2024, 9:33:26 PM</v>
       </c>
       <c r="R416" t="str">
-        <v>2020-03-26T05:36:03.701Z</v>
+        <v>2024-12-25T05:01:26.902Z</v>
       </c>
       <c r="S416" t="str">
-        <v>3/26/2020, 1:36:03 AM</v>
+        <v>12/25/2024, 12:01:26 AM</v>
       </c>
       <c r="T416">
-        <v>114</v>
+        <v>148</v>
       </c>
     </row>
     <row r="417">
       <c r="A417">
-        <v>88</v>
+        <v>384</v>
       </c>
       <c r="B417" t="str">
         <v>Nicholas Villiers</v>
@@ -26221,25 +26220,25 @@
         <v>2096922639</v>
       </c>
       <c r="F417" t="str">
-        <v>Smart Jellyfish</v>
+        <v>B2B Thyme Consequently</v>
       </c>
       <c r="G417" t="str">
-        <v>5821375</v>
+        <v>7031595</v>
       </c>
       <c r="H417" t="str">
-        <v>ZD098142</v>
+        <v/>
       </c>
       <c r="I417" t="str">
-        <v>2020-05-31T09:05:45.504Z</v>
+        <v>2025-01-23T21:42:38.460Z</v>
       </c>
       <c r="J417" t="str">
-        <v>5/31/2020, 5:05:45 AM</v>
+        <v>1/23/2025, 4:42:38 PM</v>
       </c>
       <c r="K417" t="str">
-        <v>2020-05-31T10:05:45.504Z</v>
+        <v>2025-01-23T22:42:38.460Z</v>
       </c>
       <c r="L417" t="str">
-        <v>5/31/2020, 6:05:45 AM</v>
+        <v>1/23/2025, 5:42:38 PM</v>
       </c>
       <c r="M417" t="str">
         <v>Calendar</v>
@@ -26251,24 +26250,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P417" t="str">
-        <v>2020-05-31T09:05:45.504Z</v>
+        <v>2025-01-23T21:42:38.460Z</v>
       </c>
       <c r="Q417" t="str">
-        <v>5/31/2020, 5:05:45 AM</v>
+        <v>1/23/2025, 4:42:38 PM</v>
       </c>
       <c r="R417" t="str">
-        <v>2020-05-31T10:03:45.504Z</v>
+        <v>2025-01-23T22:22:38.460Z</v>
       </c>
       <c r="S417" t="str">
-        <v>5/31/2020, 6:03:45 AM</v>
+        <v>1/23/2025, 5:22:38 PM</v>
       </c>
       <c r="T417">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="418">
       <c r="A418">
-        <v>89</v>
+        <v>385</v>
       </c>
       <c r="B418" t="str">
         <v>Nicholas Villiers</v>
@@ -26283,25 +26282,25 @@
         <v>2096922639</v>
       </c>
       <c r="F418" t="str">
-        <v>User-Centric Grimy Frugal Mmm</v>
+        <v>Revolutionary Hunt Finally Bank</v>
       </c>
       <c r="G418" t="str">
-        <v>2012145</v>
+        <v>7740219</v>
       </c>
       <c r="H418" t="str">
         <v/>
       </c>
       <c r="I418" t="str">
-        <v>2020-06-01T20:26:11.191Z</v>
+        <v>2025-02-02T03:29:23.139Z</v>
       </c>
       <c r="J418" t="str">
-        <v>6/1/2020, 4:26:11 PM</v>
+        <v>2/1/2025, 10:29:23 PM</v>
       </c>
       <c r="K418" t="str">
-        <v>2020-06-01T23:26:11.191Z</v>
+        <v>2025-02-02T06:29:23.139Z</v>
       </c>
       <c r="L418" t="str">
-        <v>6/1/2020, 7:26:11 PM</v>
+        <v>2/2/2025, 1:29:23 AM</v>
       </c>
       <c r="M418" t="str">
         <v>Calendar</v>
@@ -26313,24 +26312,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P418" t="str">
-        <v>2020-06-01T20:26:11.191Z</v>
+        <v>2025-02-02T03:29:23.139Z</v>
       </c>
       <c r="Q418" t="str">
-        <v>6/1/2020, 4:26:11 PM</v>
+        <v>2/1/2025, 10:29:23 PM</v>
       </c>
       <c r="R418" t="str">
-        <v>2020-06-01T22:00:11.191Z</v>
+        <v>2025-02-02T04:02:23.139Z</v>
       </c>
       <c r="S418" t="str">
-        <v>6/1/2020, 6:00:11 PM</v>
+        <v>2/1/2025, 11:02:23 PM</v>
       </c>
       <c r="T418">
-        <v>94</v>
+        <v>33</v>
       </c>
     </row>
     <row r="419">
       <c r="A419">
-        <v>144</v>
+        <v>435</v>
       </c>
       <c r="B419" t="str">
         <v>Nicholas Villiers</v>
@@ -26345,25 +26344,25 @@
         <v>2096922639</v>
       </c>
       <c r="F419" t="str">
-        <v>Scalable Via Vague</v>
+        <v>Best-Of-Breed Highlight</v>
       </c>
       <c r="G419" t="str">
-        <v>8803570</v>
+        <v>4665808</v>
       </c>
       <c r="H419" t="str">
-        <v>ZD498764</v>
+        <v/>
       </c>
       <c r="I419" t="str">
-        <v>2021-04-07T05:25:54.418Z</v>
+        <v>2025-11-12T20:45:18.165Z</v>
       </c>
       <c r="J419" t="str">
-        <v>4/7/2021, 1:25:54 AM</v>
+        <v>11/12/2025, 3:45:18 PM</v>
       </c>
       <c r="K419" t="str">
-        <v>2021-04-07T06:25:54.418Z</v>
+        <v>2025-11-13T00:45:18.165Z</v>
       </c>
       <c r="L419" t="str">
-        <v>4/7/2021, 2:25:54 AM</v>
+        <v>11/12/2025, 7:45:18 PM</v>
       </c>
       <c r="M419" t="str">
         <v>Calendar</v>
@@ -26375,24 +26374,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P419" t="str">
-        <v>2021-04-07T05:25:54.418Z</v>
+        <v>2025-11-12T20:45:18.165Z</v>
       </c>
       <c r="Q419" t="str">
-        <v>4/7/2021, 1:25:54 AM</v>
+        <v>11/12/2025, 3:45:18 PM</v>
       </c>
       <c r="R419" t="str">
-        <v>2021-04-07T05:58:54.418Z</v>
+        <v>2025-11-13T00:20:18.165Z</v>
       </c>
       <c r="S419" t="str">
-        <v>4/7/2021, 1:58:54 AM</v>
+        <v>11/12/2025, 7:20:18 PM</v>
       </c>
       <c r="T419">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
     <row r="420">
       <c r="A420">
-        <v>152</v>
+        <v>445</v>
       </c>
       <c r="B420" t="str">
         <v>Nicholas Villiers</v>
@@ -26407,25 +26406,25 @@
         <v>2096922639</v>
       </c>
       <c r="F420" t="str">
-        <v>Cross-Media Fatherly</v>
+        <v>Quantum For Mid Incidentally</v>
       </c>
       <c r="G420" t="str">
-        <v>3633685</v>
+        <v>2620236</v>
       </c>
       <c r="H420" t="str">
         <v/>
       </c>
       <c r="I420" t="str">
-        <v>2021-05-28T07:54:08.679Z</v>
+        <v>2025-12-29T21:55:12.556Z</v>
       </c>
       <c r="J420" t="str">
-        <v>5/28/2021, 3:54:08 AM</v>
+        <v>12/29/2025, 4:55:12 PM</v>
       </c>
       <c r="K420" t="str">
-        <v>2021-05-28T09:54:08.679Z</v>
+        <v>2025-12-30T01:55:12.556Z</v>
       </c>
       <c r="L420" t="str">
-        <v>5/28/2021, 5:54:08 AM</v>
+        <v>12/29/2025, 8:55:12 PM</v>
       </c>
       <c r="M420" t="str">
         <v>Calendar</v>
@@ -26437,1636 +26436,24 @@
         <v>Ben Hill Griffin</v>
       </c>
       <c r="P420" t="str">
-        <v>2021-05-28T07:54:08.679Z</v>
+        <v>2025-12-29T21:55:12.556Z</v>
       </c>
       <c r="Q420" t="str">
-        <v>5/28/2021, 3:54:08 AM</v>
+        <v>12/29/2025, 4:55:12 PM</v>
       </c>
       <c r="R420" t="str">
-        <v>2021-05-28T08:28:08.679Z</v>
+        <v>2025-12-29T23:15:12.556Z</v>
       </c>
       <c r="S420" t="str">
-        <v>5/28/2021, 4:28:08 AM</v>
+        <v>12/29/2025, 6:15:12 PM</v>
       </c>
       <c r="T420">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421">
-        <v>188</v>
-      </c>
-      <c r="B421" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C421" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D421" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E421" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F421" t="str">
-        <v>Frictionless Parched</v>
-      </c>
-      <c r="G421" t="str">
-        <v>1744024</v>
-      </c>
-      <c r="H421" t="str">
-        <v/>
-      </c>
-      <c r="I421" t="str">
-        <v>2021-11-22T08:12:07.299Z</v>
-      </c>
-      <c r="J421" t="str">
-        <v>11/22/2021, 3:12:07 AM</v>
-      </c>
-      <c r="K421" t="str">
-        <v>2021-11-22T09:12:07.299Z</v>
-      </c>
-      <c r="L421" t="str">
-        <v>11/22/2021, 4:12:07 AM</v>
-      </c>
-      <c r="M421" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N421" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O421" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P421" t="str">
-        <v>2021-11-22T08:12:07.299Z</v>
-      </c>
-      <c r="Q421" t="str">
-        <v>11/22/2021, 3:12:07 AM</v>
-      </c>
-      <c r="R421" t="str">
-        <v>2021-11-22T09:06:07.299Z</v>
-      </c>
-      <c r="S421" t="str">
-        <v>11/22/2021, 4:06:07 AM</v>
-      </c>
-      <c r="T421">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422">
-        <v>192</v>
-      </c>
-      <c r="B422" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C422" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D422" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E422" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F422" t="str">
-        <v>Impactful Instead Loosely</v>
-      </c>
-      <c r="G422" t="str">
-        <v>3585511</v>
-      </c>
-      <c r="H422" t="str">
-        <v/>
-      </c>
-      <c r="I422" t="str">
-        <v>2021-12-24T20:56:26.603Z</v>
-      </c>
-      <c r="J422" t="str">
-        <v>12/24/2021, 3:56:26 PM</v>
-      </c>
-      <c r="K422" t="str">
-        <v>2021-12-24T23:56:26.603Z</v>
-      </c>
-      <c r="L422" t="str">
-        <v>12/24/2021, 6:56:26 PM</v>
-      </c>
-      <c r="M422" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N422" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O422" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P422" t="str">
-        <v>2021-12-24T20:56:26.603Z</v>
-      </c>
-      <c r="Q422" t="str">
-        <v>12/24/2021, 3:56:26 PM</v>
-      </c>
-      <c r="R422" t="str">
-        <v>2021-12-24T22:38:26.603Z</v>
-      </c>
-      <c r="S422" t="str">
-        <v>12/24/2021, 5:38:26 PM</v>
-      </c>
-      <c r="T422">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423">
-        <v>194</v>
-      </c>
-      <c r="B423" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C423" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D423" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E423" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F423" t="str">
-        <v>Real-Time Provided Whose</v>
-      </c>
-      <c r="G423" t="str">
-        <v>5168421</v>
-      </c>
-      <c r="H423" t="str">
-        <v>ZD085876</v>
-      </c>
-      <c r="I423" t="str">
-        <v>2021-12-28T11:39:48.505Z</v>
-      </c>
-      <c r="J423" t="str">
-        <v>12/28/2021, 6:39:48 AM</v>
-      </c>
-      <c r="K423" t="str">
-        <v>2021-12-28T15:39:48.505Z</v>
-      </c>
-      <c r="L423" t="str">
-        <v>12/28/2021, 10:39:48 AM</v>
-      </c>
-      <c r="M423" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N423" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O423" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P423" t="str">
-        <v>2021-12-28T11:39:48.505Z</v>
-      </c>
-      <c r="Q423" t="str">
-        <v>12/28/2021, 6:39:48 AM</v>
-      </c>
-      <c r="R423" t="str">
-        <v>2021-12-28T13:15:48.505Z</v>
-      </c>
-      <c r="S423" t="str">
-        <v>12/28/2021, 8:15:48 AM</v>
-      </c>
-      <c r="T423">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424">
-        <v>201</v>
-      </c>
-      <c r="B424" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C424" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D424" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E424" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F424" t="str">
-        <v>End-To-End Optimistically</v>
-      </c>
-      <c r="G424" t="str">
-        <v>4170923</v>
-      </c>
-      <c r="H424" t="str">
-        <v/>
-      </c>
-      <c r="I424" t="str">
-        <v>2022-02-20T05:23:33.522Z</v>
-      </c>
-      <c r="J424" t="str">
-        <v>2/20/2022, 12:23:33 AM</v>
-      </c>
-      <c r="K424" t="str">
-        <v>2022-02-20T09:23:33.522Z</v>
-      </c>
-      <c r="L424" t="str">
-        <v>2/20/2022, 4:23:33 AM</v>
-      </c>
-      <c r="M424" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N424" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O424" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P424" t="str">
-        <v>2022-02-20T05:23:33.522Z</v>
-      </c>
-      <c r="Q424" t="str">
-        <v>2/20/2022, 12:23:33 AM</v>
-      </c>
-      <c r="R424" t="str">
-        <v>2022-02-20T07:30:33.522Z</v>
-      </c>
-      <c r="S424" t="str">
-        <v>2/20/2022, 2:30:33 AM</v>
-      </c>
-      <c r="T424">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425">
-        <v>211</v>
-      </c>
-      <c r="B425" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C425" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D425" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E425" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F425" t="str">
-        <v>Open-Source Whoa Energetically</v>
-      </c>
-      <c r="G425" t="str">
-        <v>8201648</v>
-      </c>
-      <c r="H425" t="str">
-        <v/>
-      </c>
-      <c r="I425" t="str">
-        <v>2022-05-10T04:32:28.755Z</v>
-      </c>
-      <c r="J425" t="str">
-        <v>5/10/2022, 12:32:28 AM</v>
-      </c>
-      <c r="K425" t="str">
-        <v>2022-05-10T06:32:28.755Z</v>
-      </c>
-      <c r="L425" t="str">
-        <v>5/10/2022, 2:32:28 AM</v>
-      </c>
-      <c r="M425" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N425" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O425" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P425" t="str">
-        <v>2022-05-10T04:32:28.755Z</v>
-      </c>
-      <c r="Q425" t="str">
-        <v>5/10/2022, 12:32:28 AM</v>
-      </c>
-      <c r="R425" t="str">
-        <v>2022-05-10T05:15:28.755Z</v>
-      </c>
-      <c r="S425" t="str">
-        <v>5/10/2022, 1:15:28 AM</v>
-      </c>
-      <c r="T425">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426">
-        <v>216</v>
-      </c>
-      <c r="B426" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C426" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D426" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E426" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F426" t="str">
-        <v>Cutting-Edge Irk Disclosure Whereas</v>
-      </c>
-      <c r="G426" t="str">
-        <v>5917518</v>
-      </c>
-      <c r="H426" t="str">
-        <v/>
-      </c>
-      <c r="I426" t="str">
-        <v>2022-05-23T10:12:17.488Z</v>
-      </c>
-      <c r="J426" t="str">
-        <v>5/23/2022, 6:12:17 AM</v>
-      </c>
-      <c r="K426" t="str">
-        <v>2022-05-23T14:12:17.488Z</v>
-      </c>
-      <c r="L426" t="str">
-        <v>5/23/2022, 10:12:17 AM</v>
-      </c>
-      <c r="M426" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N426" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O426" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P426" t="str">
-        <v>2022-05-23T10:12:17.488Z</v>
-      </c>
-      <c r="Q426" t="str">
-        <v>5/23/2022, 6:12:17 AM</v>
-      </c>
-      <c r="R426" t="str">
-        <v>2022-05-23T11:05:17.488Z</v>
-      </c>
-      <c r="S426" t="str">
-        <v>5/23/2022, 7:05:17 AM</v>
-      </c>
-      <c r="T426">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427">
-        <v>236</v>
-      </c>
-      <c r="B427" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C427" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D427" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E427" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F427" t="str">
-        <v>Decentralized Maroon Yowza Like</v>
-      </c>
-      <c r="G427" t="str">
-        <v>3783409</v>
-      </c>
-      <c r="H427" t="str">
-        <v/>
-      </c>
-      <c r="I427" t="str">
-        <v>2022-08-29T04:44:07.275Z</v>
-      </c>
-      <c r="J427" t="str">
-        <v>8/29/2022, 12:44:07 AM</v>
-      </c>
-      <c r="K427" t="str">
-        <v>2022-08-29T05:44:07.275Z</v>
-      </c>
-      <c r="L427" t="str">
-        <v>8/29/2022, 1:44:07 AM</v>
-      </c>
-      <c r="M427" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N427" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O427" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P427" t="str">
-        <v>2022-08-29T04:44:07.275Z</v>
-      </c>
-      <c r="Q427" t="str">
-        <v>8/29/2022, 12:44:07 AM</v>
-      </c>
-      <c r="R427" t="str">
-        <v>2022-08-29T05:32:07.275Z</v>
-      </c>
-      <c r="S427" t="str">
-        <v>8/29/2022, 1:32:07 AM</v>
-      </c>
-      <c r="T427">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428">
-        <v>255</v>
-      </c>
-      <c r="B428" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C428" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D428" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E428" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F428" t="str">
-        <v>Bleeding-Edge Hunger Near Recent</v>
-      </c>
-      <c r="G428" t="str">
-        <v>6998574</v>
-      </c>
-      <c r="H428" t="str">
-        <v>ZD697010</v>
-      </c>
-      <c r="I428" t="str">
-        <v>2022-12-07T18:35:11.058Z</v>
-      </c>
-      <c r="J428" t="str">
-        <v>12/7/2022, 1:35:11 PM</v>
-      </c>
-      <c r="K428" t="str">
-        <v>2022-12-07T22:35:11.058Z</v>
-      </c>
-      <c r="L428" t="str">
-        <v>12/7/2022, 5:35:11 PM</v>
-      </c>
-      <c r="M428" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N428" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O428" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P428" t="str">
-        <v>2022-12-07T18:35:11.058Z</v>
-      </c>
-      <c r="Q428" t="str">
-        <v>12/7/2022, 1:35:11 PM</v>
-      </c>
-      <c r="R428" t="str">
-        <v>2022-12-07T20:50:11.058Z</v>
-      </c>
-      <c r="S428" t="str">
-        <v>12/7/2022, 3:50:11 PM</v>
-      </c>
-      <c r="T428">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429">
-        <v>257</v>
-      </c>
-      <c r="B429" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C429" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D429" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E429" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F429" t="str">
-        <v>Strategic Psst</v>
-      </c>
-      <c r="G429" t="str">
-        <v>6544455</v>
-      </c>
-      <c r="H429" t="str">
-        <v>ZD928373</v>
-      </c>
-      <c r="I429" t="str">
-        <v>2022-12-17T14:57:48.978Z</v>
-      </c>
-      <c r="J429" t="str">
-        <v>12/17/2022, 9:57:48 AM</v>
-      </c>
-      <c r="K429" t="str">
-        <v>2022-12-17T17:57:48.978Z</v>
-      </c>
-      <c r="L429" t="str">
-        <v>12/17/2022, 12:57:48 PM</v>
-      </c>
-      <c r="M429" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N429" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O429" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P429" t="str">
-        <v>2022-12-17T14:57:48.978Z</v>
-      </c>
-      <c r="Q429" t="str">
-        <v>12/17/2022, 9:57:48 AM</v>
-      </c>
-      <c r="R429" t="str">
-        <v>2022-12-17T17:05:48.978Z</v>
-      </c>
-      <c r="S429" t="str">
-        <v>12/17/2022, 12:05:48 PM</v>
-      </c>
-      <c r="T429">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430">
-        <v>260</v>
-      </c>
-      <c r="B430" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C430" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D430" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E430" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F430" t="str">
-        <v>Efficient Warped Rapidly</v>
-      </c>
-      <c r="G430" t="str">
-        <v>1081949</v>
-      </c>
-      <c r="H430" t="str">
-        <v/>
-      </c>
-      <c r="I430" t="str">
-        <v>2023-01-07T04:35:36.436Z</v>
-      </c>
-      <c r="J430" t="str">
-        <v>1/6/2023, 11:35:36 PM</v>
-      </c>
-      <c r="K430" t="str">
-        <v>2023-01-07T07:35:36.436Z</v>
-      </c>
-      <c r="L430" t="str">
-        <v>1/7/2023, 2:35:36 AM</v>
-      </c>
-      <c r="M430" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N430" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O430" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P430" t="str">
-        <v>2023-01-07T04:35:36.436Z</v>
-      </c>
-      <c r="Q430" t="str">
-        <v>1/6/2023, 11:35:36 PM</v>
-      </c>
-      <c r="R430" t="str">
-        <v>2023-01-07T05:42:36.436Z</v>
-      </c>
-      <c r="S430" t="str">
-        <v>1/7/2023, 12:42:36 AM</v>
-      </c>
-      <c r="T430">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431">
-        <v>272</v>
-      </c>
-      <c r="B431" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C431" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D431" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E431" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F431" t="str">
-        <v>B2B Frankly Ring Fooey</v>
-      </c>
-      <c r="G431" t="str">
-        <v>7901231</v>
-      </c>
-      <c r="H431" t="str">
-        <v>ZD446960</v>
-      </c>
-      <c r="I431" t="str">
-        <v>2023-03-11T01:27:40.998Z</v>
-      </c>
-      <c r="J431" t="str">
-        <v>3/10/2023, 8:27:40 PM</v>
-      </c>
-      <c r="K431" t="str">
-        <v>2023-03-11T02:27:40.998Z</v>
-      </c>
-      <c r="L431" t="str">
-        <v>3/10/2023, 9:27:40 PM</v>
-      </c>
-      <c r="M431" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N431" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O431" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P431" t="str">
-        <v>2023-03-11T01:27:40.998Z</v>
-      </c>
-      <c r="Q431" t="str">
-        <v>3/10/2023, 8:27:40 PM</v>
-      </c>
-      <c r="R431" t="str">
-        <v>2023-03-11T02:01:40.998Z</v>
-      </c>
-      <c r="S431" t="str">
-        <v>3/10/2023, 9:01:40 PM</v>
-      </c>
-      <c r="T431">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432">
-        <v>276</v>
-      </c>
-      <c r="B432" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C432" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D432" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E432" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F432" t="str">
-        <v>B2B However</v>
-      </c>
-      <c r="G432" t="str">
-        <v>9852289</v>
-      </c>
-      <c r="H432" t="str">
-        <v>ZD123540</v>
-      </c>
-      <c r="I432" t="str">
-        <v>2023-04-14T02:13:30.363Z</v>
-      </c>
-      <c r="J432" t="str">
-        <v>4/13/2023, 10:13:30 PM</v>
-      </c>
-      <c r="K432" t="str">
-        <v>2023-04-14T03:13:30.363Z</v>
-      </c>
-      <c r="L432" t="str">
-        <v>4/13/2023, 11:13:30 PM</v>
-      </c>
-      <c r="M432" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N432" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O432" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P432" t="str">
-        <v>2023-04-14T02:13:30.363Z</v>
-      </c>
-      <c r="Q432" t="str">
-        <v>4/13/2023, 10:13:30 PM</v>
-      </c>
-      <c r="R432" t="str">
-        <v>2023-04-14T03:09:30.363Z</v>
-      </c>
-      <c r="S432" t="str">
-        <v>4/13/2023, 11:09:30 PM</v>
-      </c>
-      <c r="T432">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433">
-        <v>285</v>
-      </c>
-      <c r="B433" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C433" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D433" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E433" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F433" t="str">
-        <v>Integrated Whether Whose Supposing</v>
-      </c>
-      <c r="G433" t="str">
-        <v>4738095</v>
-      </c>
-      <c r="H433" t="str">
-        <v>ZD591142</v>
-      </c>
-      <c r="I433" t="str">
-        <v>2023-06-03T20:11:54.133Z</v>
-      </c>
-      <c r="J433" t="str">
-        <v>6/3/2023, 4:11:54 PM</v>
-      </c>
-      <c r="K433" t="str">
-        <v>2023-06-03T23:11:54.133Z</v>
-      </c>
-      <c r="L433" t="str">
-        <v>6/3/2023, 7:11:54 PM</v>
-      </c>
-      <c r="M433" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N433" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O433" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P433" t="str">
-        <v>2023-06-03T20:11:54.133Z</v>
-      </c>
-      <c r="Q433" t="str">
-        <v>6/3/2023, 4:11:54 PM</v>
-      </c>
-      <c r="R433" t="str">
-        <v>2023-06-03T21:03:54.133Z</v>
-      </c>
-      <c r="S433" t="str">
-        <v>6/3/2023, 5:03:54 PM</v>
-      </c>
-      <c r="T433">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434">
-        <v>292</v>
-      </c>
-      <c r="B434" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C434" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D434" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E434" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F434" t="str">
-        <v>Sustainable Unimpressively Quaintly</v>
-      </c>
-      <c r="G434" t="str">
-        <v>7532000</v>
-      </c>
-      <c r="H434" t="str">
-        <v/>
-      </c>
-      <c r="I434" t="str">
-        <v>2023-08-10T15:11:28.172Z</v>
-      </c>
-      <c r="J434" t="str">
-        <v>8/10/2023, 11:11:28 AM</v>
-      </c>
-      <c r="K434" t="str">
-        <v>2023-08-10T16:11:28.172Z</v>
-      </c>
-      <c r="L434" t="str">
-        <v>8/10/2023, 12:11:28 PM</v>
-      </c>
-      <c r="M434" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N434" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O434" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P434" t="str">
-        <v>2023-08-10T15:11:28.172Z</v>
-      </c>
-      <c r="Q434" t="str">
-        <v>8/10/2023, 11:11:28 AM</v>
-      </c>
-      <c r="R434" t="str">
-        <v>2023-08-10T15:46:28.172Z</v>
-      </c>
-      <c r="S434" t="str">
-        <v>8/10/2023, 11:46:28 AM</v>
-      </c>
-      <c r="T434">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435">
-        <v>294</v>
-      </c>
-      <c r="B435" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C435" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D435" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E435" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F435" t="str">
-        <v>World-Class Ha Gee Corporation</v>
-      </c>
-      <c r="G435" t="str">
-        <v>4666356</v>
-      </c>
-      <c r="H435" t="str">
-        <v/>
-      </c>
-      <c r="I435" t="str">
-        <v>2023-08-14T13:45:04.550Z</v>
-      </c>
-      <c r="J435" t="str">
-        <v>8/14/2023, 9:45:04 AM</v>
-      </c>
-      <c r="K435" t="str">
-        <v>2023-08-14T15:45:04.550Z</v>
-      </c>
-      <c r="L435" t="str">
-        <v>8/14/2023, 11:45:04 AM</v>
-      </c>
-      <c r="M435" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N435" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O435" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P435" t="str">
-        <v>2023-08-14T13:45:04.550Z</v>
-      </c>
-      <c r="Q435" t="str">
-        <v>8/14/2023, 9:45:04 AM</v>
-      </c>
-      <c r="R435" t="str">
-        <v>2023-08-14T15:16:04.550Z</v>
-      </c>
-      <c r="S435" t="str">
-        <v>8/14/2023, 11:16:04 AM</v>
-      </c>
-      <c r="T435">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436">
-        <v>295</v>
-      </c>
-      <c r="B436" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C436" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D436" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E436" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F436" t="str">
-        <v>Proactive Promptly</v>
-      </c>
-      <c r="G436" t="str">
-        <v>4791935</v>
-      </c>
-      <c r="H436" t="str">
-        <v>ZD538519</v>
-      </c>
-      <c r="I436" t="str">
-        <v>2023-08-21T23:30:42.618Z</v>
-      </c>
-      <c r="J436" t="str">
-        <v>8/21/2023, 7:30:42 PM</v>
-      </c>
-      <c r="K436" t="str">
-        <v>2023-08-22T00:30:42.618Z</v>
-      </c>
-      <c r="L436" t="str">
-        <v>8/21/2023, 8:30:42 PM</v>
-      </c>
-      <c r="M436" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N436" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O436" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P436" t="str">
-        <v>2023-08-21T23:30:42.618Z</v>
-      </c>
-      <c r="Q436" t="str">
-        <v>8/21/2023, 7:30:42 PM</v>
-      </c>
-      <c r="R436" t="str">
-        <v>2023-08-22T00:23:42.618Z</v>
-      </c>
-      <c r="S436" t="str">
-        <v>8/21/2023, 8:23:42 PM</v>
-      </c>
-      <c r="T436">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437">
-        <v>306</v>
-      </c>
-      <c r="B437" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C437" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D437" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E437" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F437" t="str">
-        <v>Mission-Critical Gracefully</v>
-      </c>
-      <c r="G437" t="str">
-        <v>3941293</v>
-      </c>
-      <c r="H437" t="str">
-        <v/>
-      </c>
-      <c r="I437" t="str">
-        <v>2023-10-18T08:16:14.947Z</v>
-      </c>
-      <c r="J437" t="str">
-        <v>10/18/2023, 4:16:14 AM</v>
-      </c>
-      <c r="K437" t="str">
-        <v>2023-10-18T11:16:14.947Z</v>
-      </c>
-      <c r="L437" t="str">
-        <v>10/18/2023, 7:16:14 AM</v>
-      </c>
-      <c r="M437" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N437" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O437" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P437" t="str">
-        <v>2023-10-18T08:16:14.947Z</v>
-      </c>
-      <c r="Q437" t="str">
-        <v>10/18/2023, 4:16:14 AM</v>
-      </c>
-      <c r="R437" t="str">
-        <v>2023-10-18T10:07:14.947Z</v>
-      </c>
-      <c r="S437" t="str">
-        <v>10/18/2023, 6:07:14 AM</v>
-      </c>
-      <c r="T437">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438">
-        <v>311</v>
-      </c>
-      <c r="B438" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C438" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D438" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E438" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F438" t="str">
-        <v>Quantum Deform</v>
-      </c>
-      <c r="G438" t="str">
-        <v>1390667</v>
-      </c>
-      <c r="H438" t="str">
-        <v>ZD439444</v>
-      </c>
-      <c r="I438" t="str">
-        <v>2023-11-11T00:58:17.243Z</v>
-      </c>
-      <c r="J438" t="str">
-        <v>11/10/2023, 7:58:17 PM</v>
-      </c>
-      <c r="K438" t="str">
-        <v>2023-11-11T04:58:17.243Z</v>
-      </c>
-      <c r="L438" t="str">
-        <v>11/10/2023, 11:58:17 PM</v>
-      </c>
-      <c r="M438" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N438" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O438" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P438" t="str">
-        <v>2023-11-11T00:58:17.243Z</v>
-      </c>
-      <c r="Q438" t="str">
-        <v>11/10/2023, 7:58:17 PM</v>
-      </c>
-      <c r="R438" t="str">
-        <v>2023-11-11T04:58:17.243Z</v>
-      </c>
-      <c r="S438" t="str">
-        <v>11/10/2023, 11:58:17 PM</v>
-      </c>
-      <c r="T438">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439">
-        <v>314</v>
-      </c>
-      <c r="B439" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C439" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D439" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E439" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F439" t="str">
-        <v>Immersive Hopeful</v>
-      </c>
-      <c r="G439" t="str">
-        <v>1113264</v>
-      </c>
-      <c r="H439" t="str">
-        <v/>
-      </c>
-      <c r="I439" t="str">
-        <v>2023-12-01T15:08:43.402Z</v>
-      </c>
-      <c r="J439" t="str">
-        <v>12/1/2023, 10:08:43 AM</v>
-      </c>
-      <c r="K439" t="str">
-        <v>2023-12-01T16:08:43.402Z</v>
-      </c>
-      <c r="L439" t="str">
-        <v>12/1/2023, 11:08:43 AM</v>
-      </c>
-      <c r="M439" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N439" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O439" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P439" t="str">
-        <v>2023-12-01T15:08:43.402Z</v>
-      </c>
-      <c r="Q439" t="str">
-        <v>12/1/2023, 10:08:43 AM</v>
-      </c>
-      <c r="R439" t="str">
-        <v>2023-12-01T16:04:43.402Z</v>
-      </c>
-      <c r="S439" t="str">
-        <v>12/1/2023, 11:04:43 AM</v>
-      </c>
-      <c r="T439">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440">
-        <v>343</v>
-      </c>
-      <c r="B440" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C440" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D440" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E440" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F440" t="str">
-        <v>B2B Poorly Good When</v>
-      </c>
-      <c r="G440" t="str">
-        <v>1241383</v>
-      </c>
-      <c r="H440" t="str">
-        <v>ZD533094</v>
-      </c>
-      <c r="I440" t="str">
-        <v>2024-05-14T01:17:12.088Z</v>
-      </c>
-      <c r="J440" t="str">
-        <v>5/13/2024, 9:17:12 PM</v>
-      </c>
-      <c r="K440" t="str">
-        <v>2024-05-14T02:17:12.088Z</v>
-      </c>
-      <c r="L440" t="str">
-        <v>5/13/2024, 10:17:12 PM</v>
-      </c>
-      <c r="M440" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N440" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O440" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P440" t="str">
-        <v>2024-05-14T01:17:12.088Z</v>
-      </c>
-      <c r="Q440" t="str">
-        <v>5/13/2024, 9:17:12 PM</v>
-      </c>
-      <c r="R440" t="str">
-        <v>2024-05-14T01:55:12.088Z</v>
-      </c>
-      <c r="S440" t="str">
-        <v>5/13/2024, 9:55:12 PM</v>
-      </c>
-      <c r="T440">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441">
-        <v>355</v>
-      </c>
-      <c r="B441" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C441" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D441" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E441" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F441" t="str">
-        <v>Sustainable Per Disrespect</v>
-      </c>
-      <c r="G441" t="str">
-        <v>1054197</v>
-      </c>
-      <c r="H441" t="str">
-        <v>ZD813098</v>
-      </c>
-      <c r="I441" t="str">
-        <v>2024-06-27T09:57:01.223Z</v>
-      </c>
-      <c r="J441" t="str">
-        <v>6/27/2024, 5:57:01 AM</v>
-      </c>
-      <c r="K441" t="str">
-        <v>2024-06-27T13:57:01.223Z</v>
-      </c>
-      <c r="L441" t="str">
-        <v>6/27/2024, 9:57:01 AM</v>
-      </c>
-      <c r="M441" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N441" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O441" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P441" t="str">
-        <v>2024-06-27T09:57:01.223Z</v>
-      </c>
-      <c r="Q441" t="str">
-        <v>6/27/2024, 5:57:01 AM</v>
-      </c>
-      <c r="R441" t="str">
-        <v>2024-06-27T11:17:01.223Z</v>
-      </c>
-      <c r="S441" t="str">
-        <v>6/27/2024, 7:17:01 AM</v>
-      </c>
-      <c r="T441">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442">
-        <v>381</v>
-      </c>
-      <c r="B442" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C442" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D442" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E442" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F442" t="str">
-        <v>Collaborative Noted Er Boo</v>
-      </c>
-      <c r="G442" t="str">
-        <v>4990954</v>
-      </c>
-      <c r="H442" t="str">
-        <v>ZD895021</v>
-      </c>
-      <c r="I442" t="str">
-        <v>2024-12-25T02:33:26.902Z</v>
-      </c>
-      <c r="J442" t="str">
-        <v>12/24/2024, 9:33:26 PM</v>
-      </c>
-      <c r="K442" t="str">
-        <v>2024-12-25T05:33:26.902Z</v>
-      </c>
-      <c r="L442" t="str">
-        <v>12/25/2024, 12:33:26 AM</v>
-      </c>
-      <c r="M442" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N442" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O442" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P442" t="str">
-        <v>2024-12-25T02:33:26.902Z</v>
-      </c>
-      <c r="Q442" t="str">
-        <v>12/24/2024, 9:33:26 PM</v>
-      </c>
-      <c r="R442" t="str">
-        <v>2024-12-25T05:01:26.902Z</v>
-      </c>
-      <c r="S442" t="str">
-        <v>12/25/2024, 12:01:26 AM</v>
-      </c>
-      <c r="T442">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443">
-        <v>384</v>
-      </c>
-      <c r="B443" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C443" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D443" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E443" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F443" t="str">
-        <v>B2B Thyme Consequently</v>
-      </c>
-      <c r="G443" t="str">
-        <v>7031595</v>
-      </c>
-      <c r="H443" t="str">
-        <v/>
-      </c>
-      <c r="I443" t="str">
-        <v>2025-01-23T21:42:38.460Z</v>
-      </c>
-      <c r="J443" t="str">
-        <v>1/23/2025, 4:42:38 PM</v>
-      </c>
-      <c r="K443" t="str">
-        <v>2025-01-23T22:42:38.460Z</v>
-      </c>
-      <c r="L443" t="str">
-        <v>1/23/2025, 5:42:38 PM</v>
-      </c>
-      <c r="M443" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N443" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O443" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P443" t="str">
-        <v>2025-01-23T21:42:38.460Z</v>
-      </c>
-      <c r="Q443" t="str">
-        <v>1/23/2025, 4:42:38 PM</v>
-      </c>
-      <c r="R443" t="str">
-        <v>2025-01-23T22:22:38.460Z</v>
-      </c>
-      <c r="S443" t="str">
-        <v>1/23/2025, 5:22:38 PM</v>
-      </c>
-      <c r="T443">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444">
-        <v>385</v>
-      </c>
-      <c r="B444" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C444" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D444" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E444" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F444" t="str">
-        <v>Revolutionary Hunt Finally Bank</v>
-      </c>
-      <c r="G444" t="str">
-        <v>7740219</v>
-      </c>
-      <c r="H444" t="str">
-        <v/>
-      </c>
-      <c r="I444" t="str">
-        <v>2025-02-02T03:29:23.139Z</v>
-      </c>
-      <c r="J444" t="str">
-        <v>2/1/2025, 10:29:23 PM</v>
-      </c>
-      <c r="K444" t="str">
-        <v>2025-02-02T06:29:23.139Z</v>
-      </c>
-      <c r="L444" t="str">
-        <v>2/2/2025, 1:29:23 AM</v>
-      </c>
-      <c r="M444" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N444" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O444" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P444" t="str">
-        <v>2025-02-02T03:29:23.139Z</v>
-      </c>
-      <c r="Q444" t="str">
-        <v>2/1/2025, 10:29:23 PM</v>
-      </c>
-      <c r="R444" t="str">
-        <v>2025-02-02T04:02:23.139Z</v>
-      </c>
-      <c r="S444" t="str">
-        <v>2/1/2025, 11:02:23 PM</v>
-      </c>
-      <c r="T444">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445">
-        <v>435</v>
-      </c>
-      <c r="B445" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C445" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D445" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E445" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F445" t="str">
-        <v>Best-Of-Breed Highlight</v>
-      </c>
-      <c r="G445" t="str">
-        <v>4665808</v>
-      </c>
-      <c r="H445" t="str">
-        <v/>
-      </c>
-      <c r="I445" t="str">
-        <v>2025-11-12T20:45:18.165Z</v>
-      </c>
-      <c r="J445" t="str">
-        <v>11/12/2025, 3:45:18 PM</v>
-      </c>
-      <c r="K445" t="str">
-        <v>2025-11-13T00:45:18.165Z</v>
-      </c>
-      <c r="L445" t="str">
-        <v>11/12/2025, 7:45:18 PM</v>
-      </c>
-      <c r="M445" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N445" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O445" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P445" t="str">
-        <v>2025-11-12T20:45:18.165Z</v>
-      </c>
-      <c r="Q445" t="str">
-        <v>11/12/2025, 3:45:18 PM</v>
-      </c>
-      <c r="R445" t="str">
-        <v>2025-11-13T00:20:18.165Z</v>
-      </c>
-      <c r="S445" t="str">
-        <v>11/12/2025, 7:20:18 PM</v>
-      </c>
-      <c r="T445">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446">
-        <v>445</v>
-      </c>
-      <c r="B446" t="str">
-        <v>Nicholas Villiers</v>
-      </c>
-      <c r="C446" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="D446" t="str">
-        <v>nickvboy@gmail.com</v>
-      </c>
-      <c r="E446" t="str">
-        <v>2096922639</v>
-      </c>
-      <c r="F446" t="str">
-        <v>Quantum For Mid Incidentally</v>
-      </c>
-      <c r="G446" t="str">
-        <v>2620236</v>
-      </c>
-      <c r="H446" t="str">
-        <v/>
-      </c>
-      <c r="I446" t="str">
-        <v>2025-12-29T21:55:12.556Z</v>
-      </c>
-      <c r="J446" t="str">
-        <v>12/29/2025, 4:55:12 PM</v>
-      </c>
-      <c r="K446" t="str">
-        <v>2025-12-30T01:55:12.556Z</v>
-      </c>
-      <c r="L446" t="str">
-        <v>12/29/2025, 8:55:12 PM</v>
-      </c>
-      <c r="M446" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N446" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O446" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P446" t="str">
-        <v>2025-12-29T21:55:12.556Z</v>
-      </c>
-      <c r="Q446" t="str">
-        <v>12/29/2025, 4:55:12 PM</v>
-      </c>
-      <c r="R446" t="str">
-        <v>2025-12-29T23:15:12.556Z</v>
-      </c>
-      <c r="S446" t="str">
-        <v>12/29/2025, 6:15:12 PM</v>
-      </c>
-      <c r="T446">
         <v>80</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T446"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T420"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -32807,1691 +31194,6 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T27"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Log ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>User Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>User Email</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Profile Email</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Profile Phone</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Event Title</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Event Code</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Zendesk Ticket</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Event Start</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Event Start (Local)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Event End</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Event End (Local)</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Location</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Building</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Logged Start</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Logged Start (Local)</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Logged End</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Logged End (Local)</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Duration Minutes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>8</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C2" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D2" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E2" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Granular Midst Perky Everlasting</v>
-      </c>
-      <c r="G2" t="str">
-        <v>7587773</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>2019-02-10T16:38:01.088Z</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2/10/2019, 11:38:01 AM</v>
-      </c>
-      <c r="K2" t="str">
-        <v>2019-02-10T19:38:01.088Z</v>
-      </c>
-      <c r="L2" t="str">
-        <v>2/10/2019, 2:38:01 PM</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N2" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P2" t="str">
-        <v>2019-02-10T16:38:01.088Z</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>2/10/2019, 11:38:01 AM</v>
-      </c>
-      <c r="R2" t="str">
-        <v>2019-02-10T19:11:01.088Z</v>
-      </c>
-      <c r="S2" t="str">
-        <v>2/10/2019, 2:11:01 PM</v>
-      </c>
-      <c r="T2">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>39</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C3" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D3" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E3" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Synergistic Quit Trek But</v>
-      </c>
-      <c r="G3" t="str">
-        <v>1448827</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>2019-09-26T07:04:01.022Z</v>
-      </c>
-      <c r="J3" t="str">
-        <v>9/26/2019, 3:04:01 AM</v>
-      </c>
-      <c r="K3" t="str">
-        <v>2019-09-26T09:04:01.022Z</v>
-      </c>
-      <c r="L3" t="str">
-        <v>9/26/2019, 5:04:01 AM</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N3" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P3" t="str">
-        <v>2019-09-26T07:04:01.022Z</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>9/26/2019, 3:04:01 AM</v>
-      </c>
-      <c r="R3" t="str">
-        <v>2019-09-26T08:03:01.022Z</v>
-      </c>
-      <c r="S3" t="str">
-        <v>9/26/2019, 4:03:01 AM</v>
-      </c>
-      <c r="T3">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>55</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C4" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D4" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E4" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Impactful Unimpressively</v>
-      </c>
-      <c r="G4" t="str">
-        <v>8687107</v>
-      </c>
-      <c r="H4" t="str">
-        <v>ZD155686</v>
-      </c>
-      <c r="I4" t="str">
-        <v>2019-11-23T22:56:47.005Z</v>
-      </c>
-      <c r="J4" t="str">
-        <v>11/23/2019, 5:56:47 PM</v>
-      </c>
-      <c r="K4" t="str">
-        <v>2019-11-24T02:56:47.005Z</v>
-      </c>
-      <c r="L4" t="str">
-        <v>11/23/2019, 9:56:47 PM</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N4" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P4" t="str">
-        <v>2019-11-23T22:56:47.005Z</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>11/23/2019, 5:56:47 PM</v>
-      </c>
-      <c r="R4" t="str">
-        <v>2019-11-24T01:11:47.005Z</v>
-      </c>
-      <c r="S4" t="str">
-        <v>11/23/2019, 8:11:47 PM</v>
-      </c>
-      <c r="T4">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>63</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C5" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D5" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E5" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Plug-And-Play Nun</v>
-      </c>
-      <c r="G5" t="str">
-        <v>8055884</v>
-      </c>
-      <c r="H5" t="str">
-        <v>ZD061746</v>
-      </c>
-      <c r="I5" t="str">
-        <v>2020-01-08T18:32:37.824Z</v>
-      </c>
-      <c r="J5" t="str">
-        <v>1/8/2020, 1:32:37 PM</v>
-      </c>
-      <c r="K5" t="str">
-        <v>2020-01-08T20:32:37.824Z</v>
-      </c>
-      <c r="L5" t="str">
-        <v>1/8/2020, 3:32:37 PM</v>
-      </c>
-      <c r="M5" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N5" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O5" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P5" t="str">
-        <v>2020-01-08T18:32:37.824Z</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>1/8/2020, 1:32:37 PM</v>
-      </c>
-      <c r="R5" t="str">
-        <v>2020-01-08T19:39:37.824Z</v>
-      </c>
-      <c r="S5" t="str">
-        <v>1/8/2020, 2:39:37 PM</v>
-      </c>
-      <c r="T5">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>105</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C6" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D6" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E6" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Plug-And-Play Yum Versus Yowza</v>
-      </c>
-      <c r="G6" t="str">
-        <v>1183382</v>
-      </c>
-      <c r="H6" t="str">
-        <v>ZD455800</v>
-      </c>
-      <c r="I6" t="str">
-        <v>2020-09-04T01:37:54.128Z</v>
-      </c>
-      <c r="J6" t="str">
-        <v>9/3/2020, 9:37:54 PM</v>
-      </c>
-      <c r="K6" t="str">
-        <v>2020-09-04T03:37:54.128Z</v>
-      </c>
-      <c r="L6" t="str">
-        <v>9/3/2020, 11:37:54 PM</v>
-      </c>
-      <c r="M6" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N6" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O6" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P6" t="str">
-        <v>2020-09-04T01:37:54.128Z</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>9/3/2020, 9:37:54 PM</v>
-      </c>
-      <c r="R6" t="str">
-        <v>2020-09-04T03:32:54.128Z</v>
-      </c>
-      <c r="S6" t="str">
-        <v>9/3/2020, 11:32:54 PM</v>
-      </c>
-      <c r="T6">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>106</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C7" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D7" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E7" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Value-Added Upon</v>
-      </c>
-      <c r="G7" t="str">
-        <v>6110501</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>2020-09-09T18:53:33.138Z</v>
-      </c>
-      <c r="J7" t="str">
-        <v>9/9/2020, 2:53:33 PM</v>
-      </c>
-      <c r="K7" t="str">
-        <v>2020-09-09T19:53:33.138Z</v>
-      </c>
-      <c r="L7" t="str">
-        <v>9/9/2020, 3:53:33 PM</v>
-      </c>
-      <c r="M7" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N7" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O7" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P7" t="str">
-        <v>2020-09-09T18:53:33.138Z</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>9/9/2020, 2:53:33 PM</v>
-      </c>
-      <c r="R7" t="str">
-        <v>2020-09-09T19:51:33.138Z</v>
-      </c>
-      <c r="S7" t="str">
-        <v>9/9/2020, 3:51:33 PM</v>
-      </c>
-      <c r="T7">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>127</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C8" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D8" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E8" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Cutting-Edge Amid Which Uh-Huh</v>
-      </c>
-      <c r="G8" t="str">
-        <v>9499602</v>
-      </c>
-      <c r="H8" t="str">
-        <v>ZD830328</v>
-      </c>
-      <c r="I8" t="str">
-        <v>2021-01-14T17:28:48.397Z</v>
-      </c>
-      <c r="J8" t="str">
-        <v>1/14/2021, 12:28:48 PM</v>
-      </c>
-      <c r="K8" t="str">
-        <v>2021-01-14T19:28:48.397Z</v>
-      </c>
-      <c r="L8" t="str">
-        <v>1/14/2021, 2:28:48 PM</v>
-      </c>
-      <c r="M8" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N8" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P8" t="str">
-        <v>2021-01-14T17:28:48.397Z</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>1/14/2021, 12:28:48 PM</v>
-      </c>
-      <c r="R8" t="str">
-        <v>2021-01-14T18:34:48.397Z</v>
-      </c>
-      <c r="S8" t="str">
-        <v>1/14/2021, 1:34:48 PM</v>
-      </c>
-      <c r="T8">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>129</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C9" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D9" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E9" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Strategic Loosely Along Spherical</v>
-      </c>
-      <c r="G9" t="str">
-        <v>3192905</v>
-      </c>
-      <c r="H9" t="str">
-        <v>ZD041990</v>
-      </c>
-      <c r="I9" t="str">
-        <v>2021-01-27T00:36:18.569Z</v>
-      </c>
-      <c r="J9" t="str">
-        <v>1/26/2021, 7:36:18 PM</v>
-      </c>
-      <c r="K9" t="str">
-        <v>2021-01-27T04:36:18.569Z</v>
-      </c>
-      <c r="L9" t="str">
-        <v>1/26/2021, 11:36:18 PM</v>
-      </c>
-      <c r="M9" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N9" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O9" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P9" t="str">
-        <v>2021-01-27T00:36:18.569Z</v>
-      </c>
-      <c r="Q9" t="str">
-        <v>1/26/2021, 7:36:18 PM</v>
-      </c>
-      <c r="R9" t="str">
-        <v>2021-01-27T04:34:18.569Z</v>
-      </c>
-      <c r="S9" t="str">
-        <v>1/26/2021, 11:34:18 PM</v>
-      </c>
-      <c r="T9">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>155</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C10" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D10" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E10" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Real-Time Ew</v>
-      </c>
-      <c r="G10" t="str">
-        <v>2846707</v>
-      </c>
-      <c r="H10" t="str">
-        <v>ZD166749</v>
-      </c>
-      <c r="I10" t="str">
-        <v>2021-06-20T00:42:53.876Z</v>
-      </c>
-      <c r="J10" t="str">
-        <v>6/19/2021, 8:42:53 PM</v>
-      </c>
-      <c r="K10" t="str">
-        <v>2021-06-20T03:42:53.876Z</v>
-      </c>
-      <c r="L10" t="str">
-        <v>6/19/2021, 11:42:53 PM</v>
-      </c>
-      <c r="M10" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N10" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O10" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P10" t="str">
-        <v>2021-06-20T00:42:53.876Z</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>6/19/2021, 8:42:53 PM</v>
-      </c>
-      <c r="R10" t="str">
-        <v>2021-06-20T02:32:53.876Z</v>
-      </c>
-      <c r="S10" t="str">
-        <v>6/19/2021, 10:32:53 PM</v>
-      </c>
-      <c r="T10">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>208</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C11" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D11" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E11" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Sticky Which</v>
-      </c>
-      <c r="G11" t="str">
-        <v>8124639</v>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>2022-04-10T08:53:38.723Z</v>
-      </c>
-      <c r="J11" t="str">
-        <v>4/10/2022, 4:53:38 AM</v>
-      </c>
-      <c r="K11" t="str">
-        <v>2022-04-10T09:53:38.723Z</v>
-      </c>
-      <c r="L11" t="str">
-        <v>4/10/2022, 5:53:38 AM</v>
-      </c>
-      <c r="M11" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N11" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O11" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P11" t="str">
-        <v>2022-04-10T08:53:38.723Z</v>
-      </c>
-      <c r="Q11" t="str">
-        <v>4/10/2022, 4:53:38 AM</v>
-      </c>
-      <c r="R11" t="str">
-        <v>2022-04-10T09:43:38.723Z</v>
-      </c>
-      <c r="S11" t="str">
-        <v>4/10/2022, 5:43:38 AM</v>
-      </c>
-      <c r="T11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>213</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C12" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D12" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E12" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Impactful Yuck Via</v>
-      </c>
-      <c r="G12" t="str">
-        <v>6452102</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>2022-05-12T04:19:37.907Z</v>
-      </c>
-      <c r="J12" t="str">
-        <v>5/12/2022, 12:19:37 AM</v>
-      </c>
-      <c r="K12" t="str">
-        <v>2022-05-12T06:19:37.907Z</v>
-      </c>
-      <c r="L12" t="str">
-        <v>5/12/2022, 2:19:37 AM</v>
-      </c>
-      <c r="M12" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N12" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O12" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P12" t="str">
-        <v>2022-05-12T04:19:37.907Z</v>
-      </c>
-      <c r="Q12" t="str">
-        <v>5/12/2022, 12:19:37 AM</v>
-      </c>
-      <c r="R12" t="str">
-        <v>2022-05-12T05:23:37.907Z</v>
-      </c>
-      <c r="S12" t="str">
-        <v>5/12/2022, 1:23:37 AM</v>
-      </c>
-      <c r="T12">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>215</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C13" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D13" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E13" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Best-Of-Breed Hopelessly Gracious</v>
-      </c>
-      <c r="G13" t="str">
-        <v>1895485</v>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>2022-05-19T20:48:04.893Z</v>
-      </c>
-      <c r="J13" t="str">
-        <v>5/19/2022, 4:48:04 PM</v>
-      </c>
-      <c r="K13" t="str">
-        <v>2022-05-20T00:48:04.893Z</v>
-      </c>
-      <c r="L13" t="str">
-        <v>5/19/2022, 8:48:04 PM</v>
-      </c>
-      <c r="M13" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N13" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O13" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P13" t="str">
-        <v>2022-05-19T20:48:04.893Z</v>
-      </c>
-      <c r="Q13" t="str">
-        <v>5/19/2022, 4:48:04 PM</v>
-      </c>
-      <c r="R13" t="str">
-        <v>2022-05-19T22:40:04.893Z</v>
-      </c>
-      <c r="S13" t="str">
-        <v>5/19/2022, 6:40:04 PM</v>
-      </c>
-      <c r="T13">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>230</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C14" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D14" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E14" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Mission-Critical Below King</v>
-      </c>
-      <c r="G14" t="str">
-        <v>1503395</v>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>2022-08-08T05:58:26.201Z</v>
-      </c>
-      <c r="J14" t="str">
-        <v>8/8/2022, 1:58:26 AM</v>
-      </c>
-      <c r="K14" t="str">
-        <v>2022-08-08T09:58:26.201Z</v>
-      </c>
-      <c r="L14" t="str">
-        <v>8/8/2022, 5:58:26 AM</v>
-      </c>
-      <c r="M14" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N14" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O14" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P14" t="str">
-        <v>2022-08-08T05:58:26.201Z</v>
-      </c>
-      <c r="Q14" t="str">
-        <v>8/8/2022, 1:58:26 AM</v>
-      </c>
-      <c r="R14" t="str">
-        <v>2022-08-08T09:20:26.201Z</v>
-      </c>
-      <c r="S14" t="str">
-        <v>8/8/2022, 5:20:26 AM</v>
-      </c>
-      <c r="T14">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>254</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C15" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D15" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E15" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Innovative Via Oof</v>
-      </c>
-      <c r="G15" t="str">
-        <v>1282539</v>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>2022-12-07T10:20:47.037Z</v>
-      </c>
-      <c r="J15" t="str">
-        <v>12/7/2022, 5:20:47 AM</v>
-      </c>
-      <c r="K15" t="str">
-        <v>2022-12-07T14:20:47.037Z</v>
-      </c>
-      <c r="L15" t="str">
-        <v>12/7/2022, 9:20:47 AM</v>
-      </c>
-      <c r="M15" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N15" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O15" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P15" t="str">
-        <v>2022-12-07T10:20:47.037Z</v>
-      </c>
-      <c r="Q15" t="str">
-        <v>12/7/2022, 5:20:47 AM</v>
-      </c>
-      <c r="R15" t="str">
-        <v>2022-12-07T11:43:47.037Z</v>
-      </c>
-      <c r="S15" t="str">
-        <v>12/7/2022, 6:43:47 AM</v>
-      </c>
-      <c r="T15">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>280</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C16" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D16" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E16" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Integrated Now Unfortunately Finally</v>
-      </c>
-      <c r="G16" t="str">
-        <v>1514032</v>
-      </c>
-      <c r="H16" t="str">
-        <v>ZD088506</v>
-      </c>
-      <c r="I16" t="str">
-        <v>2023-05-07T01:21:51.191Z</v>
-      </c>
-      <c r="J16" t="str">
-        <v>5/6/2023, 9:21:51 PM</v>
-      </c>
-      <c r="K16" t="str">
-        <v>2023-05-07T02:21:51.191Z</v>
-      </c>
-      <c r="L16" t="str">
-        <v>5/6/2023, 10:21:51 PM</v>
-      </c>
-      <c r="M16" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N16" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O16" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P16" t="str">
-        <v>2023-05-07T01:21:51.191Z</v>
-      </c>
-      <c r="Q16" t="str">
-        <v>5/6/2023, 9:21:51 PM</v>
-      </c>
-      <c r="R16" t="str">
-        <v>2023-05-07T02:10:51.191Z</v>
-      </c>
-      <c r="S16" t="str">
-        <v>5/6/2023, 10:10:51 PM</v>
-      </c>
-      <c r="T16">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>281</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C17" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D17" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E17" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F17" t="str">
-        <v>One-To-One Yum</v>
-      </c>
-      <c r="G17" t="str">
-        <v>1095875</v>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>2023-05-09T10:38:56.764Z</v>
-      </c>
-      <c r="J17" t="str">
-        <v>5/9/2023, 6:38:56 AM</v>
-      </c>
-      <c r="K17" t="str">
-        <v>2023-05-09T12:38:56.764Z</v>
-      </c>
-      <c r="L17" t="str">
-        <v>5/9/2023, 8:38:56 AM</v>
-      </c>
-      <c r="M17" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N17" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O17" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P17" t="str">
-        <v>2023-05-09T10:38:56.764Z</v>
-      </c>
-      <c r="Q17" t="str">
-        <v>5/9/2023, 6:38:56 AM</v>
-      </c>
-      <c r="R17" t="str">
-        <v>2023-05-09T11:30:56.764Z</v>
-      </c>
-      <c r="S17" t="str">
-        <v>5/9/2023, 7:30:56 AM</v>
-      </c>
-      <c r="T17">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>291</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C18" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D18" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E18" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Out-Of-The-Box Glisten Appreciate</v>
-      </c>
-      <c r="G18" t="str">
-        <v>4196463</v>
-      </c>
-      <c r="H18" t="str">
-        <v>ZD261108</v>
-      </c>
-      <c r="I18" t="str">
-        <v>2023-08-02T22:20:22.482Z</v>
-      </c>
-      <c r="J18" t="str">
-        <v>8/2/2023, 6:20:22 PM</v>
-      </c>
-      <c r="K18" t="str">
-        <v>2023-08-03T01:20:22.482Z</v>
-      </c>
-      <c r="L18" t="str">
-        <v>8/2/2023, 9:20:22 PM</v>
-      </c>
-      <c r="M18" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N18" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O18" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P18" t="str">
-        <v>2023-08-02T22:20:22.482Z</v>
-      </c>
-      <c r="Q18" t="str">
-        <v>8/2/2023, 6:20:22 PM</v>
-      </c>
-      <c r="R18" t="str">
-        <v>2023-08-02T22:59:22.482Z</v>
-      </c>
-      <c r="S18" t="str">
-        <v>8/2/2023, 6:59:22 PM</v>
-      </c>
-      <c r="T18">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>326</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C19" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D19" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E19" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Interactive Abandoned Fork</v>
-      </c>
-      <c r="G19" t="str">
-        <v>3817938</v>
-      </c>
-      <c r="H19" t="str">
-        <v>ZD459340</v>
-      </c>
-      <c r="I19" t="str">
-        <v>2024-01-31T18:27:56.360Z</v>
-      </c>
-      <c r="J19" t="str">
-        <v>1/31/2024, 1:27:56 PM</v>
-      </c>
-      <c r="K19" t="str">
-        <v>2024-01-31T20:27:56.360Z</v>
-      </c>
-      <c r="L19" t="str">
-        <v>1/31/2024, 3:27:56 PM</v>
-      </c>
-      <c r="M19" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N19" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O19" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P19" t="str">
-        <v>2024-01-31T18:27:56.360Z</v>
-      </c>
-      <c r="Q19" t="str">
-        <v>1/31/2024, 1:27:56 PM</v>
-      </c>
-      <c r="R19" t="str">
-        <v>2024-01-31T20:15:56.360Z</v>
-      </c>
-      <c r="S19" t="str">
-        <v>1/31/2024, 3:15:56 PM</v>
-      </c>
-      <c r="T19">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>330</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C20" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D20" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E20" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F20" t="str">
-        <v>End-To-End Psst Scale Potable</v>
-      </c>
-      <c r="G20" t="str">
-        <v>8250420</v>
-      </c>
-      <c r="H20" t="str">
-        <v>ZD638232</v>
-      </c>
-      <c r="I20" t="str">
-        <v>2024-02-25T10:48:14.703Z</v>
-      </c>
-      <c r="J20" t="str">
-        <v>2/25/2024, 5:48:14 AM</v>
-      </c>
-      <c r="K20" t="str">
-        <v>2024-02-25T13:48:14.703Z</v>
-      </c>
-      <c r="L20" t="str">
-        <v>2/25/2024, 8:48:14 AM</v>
-      </c>
-      <c r="M20" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N20" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O20" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P20" t="str">
-        <v>2024-02-25T10:48:14.703Z</v>
-      </c>
-      <c r="Q20" t="str">
-        <v>2/25/2024, 5:48:14 AM</v>
-      </c>
-      <c r="R20" t="str">
-        <v>2024-02-25T12:34:14.703Z</v>
-      </c>
-      <c r="S20" t="str">
-        <v>2/25/2024, 7:34:14 AM</v>
-      </c>
-      <c r="T20">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>354</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C21" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D21" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E21" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Synergistic Sauerkraut</v>
-      </c>
-      <c r="G21" t="str">
-        <v>1807857</v>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v>2024-06-25T21:53:06.886Z</v>
-      </c>
-      <c r="J21" t="str">
-        <v>6/25/2024, 5:53:06 PM</v>
-      </c>
-      <c r="K21" t="str">
-        <v>2024-06-26T01:53:06.886Z</v>
-      </c>
-      <c r="L21" t="str">
-        <v>6/25/2024, 9:53:06 PM</v>
-      </c>
-      <c r="M21" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N21" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O21" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P21" t="str">
-        <v>2024-06-25T21:53:06.886Z</v>
-      </c>
-      <c r="Q21" t="str">
-        <v>6/25/2024, 5:53:06 PM</v>
-      </c>
-      <c r="R21" t="str">
-        <v>2024-06-25T23:32:06.886Z</v>
-      </c>
-      <c r="S21" t="str">
-        <v>6/25/2024, 7:32:06 PM</v>
-      </c>
-      <c r="T21">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>361</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C22" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D22" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E22" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Seamless Provided</v>
-      </c>
-      <c r="G22" t="str">
-        <v>8181010</v>
-      </c>
-      <c r="H22" t="str">
-        <v>ZD981702</v>
-      </c>
-      <c r="I22" t="str">
-        <v>2024-08-19T23:42:33.805Z</v>
-      </c>
-      <c r="J22" t="str">
-        <v>8/19/2024, 7:42:33 PM</v>
-      </c>
-      <c r="K22" t="str">
-        <v>2024-08-20T02:42:33.805Z</v>
-      </c>
-      <c r="L22" t="str">
-        <v>8/19/2024, 10:42:33 PM</v>
-      </c>
-      <c r="M22" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N22" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O22" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P22" t="str">
-        <v>2024-08-19T23:42:33.805Z</v>
-      </c>
-      <c r="Q22" t="str">
-        <v>8/19/2024, 7:42:33 PM</v>
-      </c>
-      <c r="R22" t="str">
-        <v>2024-08-20T02:21:33.805Z</v>
-      </c>
-      <c r="S22" t="str">
-        <v>8/19/2024, 10:21:33 PM</v>
-      </c>
-      <c r="T22">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>390</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C23" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D23" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E23" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F23" t="str">
-        <v>B2C Masquerade</v>
-      </c>
-      <c r="G23" t="str">
-        <v>6093737</v>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v>2025-02-28T03:10:22.755Z</v>
-      </c>
-      <c r="J23" t="str">
-        <v>2/27/2025, 10:10:22 PM</v>
-      </c>
-      <c r="K23" t="str">
-        <v>2025-02-28T07:10:22.755Z</v>
-      </c>
-      <c r="L23" t="str">
-        <v>2/28/2025, 2:10:22 AM</v>
-      </c>
-      <c r="M23" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N23" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O23" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P23" t="str">
-        <v>2025-02-28T03:10:22.755Z</v>
-      </c>
-      <c r="Q23" t="str">
-        <v>2/27/2025, 10:10:22 PM</v>
-      </c>
-      <c r="R23" t="str">
-        <v>2025-02-28T05:45:22.755Z</v>
-      </c>
-      <c r="S23" t="str">
-        <v>2/28/2025, 12:45:22 AM</v>
-      </c>
-      <c r="T23">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>406</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C24" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D24" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E24" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Extensible Retrospectivity</v>
-      </c>
-      <c r="G24" t="str">
-        <v>8578458</v>
-      </c>
-      <c r="H24" t="str">
-        <v>ZD837236</v>
-      </c>
-      <c r="I24" t="str">
-        <v>2025-05-29T00:12:48.889Z</v>
-      </c>
-      <c r="J24" t="str">
-        <v>5/28/2025, 8:12:48 PM</v>
-      </c>
-      <c r="K24" t="str">
-        <v>2025-05-29T04:12:48.889Z</v>
-      </c>
-      <c r="L24" t="str">
-        <v>5/29/2025, 12:12:48 AM</v>
-      </c>
-      <c r="M24" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N24" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O24" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P24" t="str">
-        <v>2025-05-29T00:12:48.889Z</v>
-      </c>
-      <c r="Q24" t="str">
-        <v>5/28/2025, 8:12:48 PM</v>
-      </c>
-      <c r="R24" t="str">
-        <v>2025-05-29T01:37:48.889Z</v>
-      </c>
-      <c r="S24" t="str">
-        <v>5/28/2025, 9:37:48 PM</v>
-      </c>
-      <c r="T24">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>409</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C25" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D25" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E25" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F25" t="str">
-        <v>Back-End Numeric</v>
-      </c>
-      <c r="G25" t="str">
-        <v>5140781</v>
-      </c>
-      <c r="H25" t="str">
-        <v>ZD297884</v>
-      </c>
-      <c r="I25" t="str">
-        <v>2025-06-10T02:56:47.250Z</v>
-      </c>
-      <c r="J25" t="str">
-        <v>6/9/2025, 10:56:47 PM</v>
-      </c>
-      <c r="K25" t="str">
-        <v>2025-06-10T04:56:47.250Z</v>
-      </c>
-      <c r="L25" t="str">
-        <v>6/10/2025, 12:56:47 AM</v>
-      </c>
-      <c r="M25" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N25" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O25" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P25" t="str">
-        <v>2025-06-10T02:56:47.250Z</v>
-      </c>
-      <c r="Q25" t="str">
-        <v>6/9/2025, 10:56:47 PM</v>
-      </c>
-      <c r="R25" t="str">
-        <v>2025-06-10T03:51:47.250Z</v>
-      </c>
-      <c r="S25" t="str">
-        <v>6/9/2025, 11:51:47 PM</v>
-      </c>
-      <c r="T25">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>417</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C26" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D26" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E26" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F26" t="str">
-        <v>One-To-One Impossible Crumble Affectionate</v>
-      </c>
-      <c r="G26" t="str">
-        <v>5783731</v>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v>2025-07-03T08:17:13.878Z</v>
-      </c>
-      <c r="J26" t="str">
-        <v>7/3/2025, 4:17:13 AM</v>
-      </c>
-      <c r="K26" t="str">
-        <v>2025-07-03T09:17:13.878Z</v>
-      </c>
-      <c r="L26" t="str">
-        <v>7/3/2025, 5:17:13 AM</v>
-      </c>
-      <c r="M26" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N26" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O26" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P26" t="str">
-        <v>2025-07-03T08:17:13.878Z</v>
-      </c>
-      <c r="Q26" t="str">
-        <v>7/3/2025, 4:17:13 AM</v>
-      </c>
-      <c r="R26" t="str">
-        <v>2025-07-03T09:07:13.878Z</v>
-      </c>
-      <c r="S26" t="str">
-        <v>7/3/2025, 5:07:13 AM</v>
-      </c>
-      <c r="T26">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>423</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Miller Mayert</v>
-      </c>
-      <c r="C27" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="D27" t="str">
-        <v>manager-millermayert-1@fgcu.local</v>
-      </c>
-      <c r="E27" t="str">
-        <v>4456102911</v>
-      </c>
-      <c r="F27" t="str">
-        <v>Back-End Loftily Horn Noteworthy</v>
-      </c>
-      <c r="G27" t="str">
-        <v>7432112</v>
-      </c>
-      <c r="H27" t="str">
-        <v>ZD599982</v>
-      </c>
-      <c r="I27" t="str">
-        <v>2025-08-03T06:39:16.333Z</v>
-      </c>
-      <c r="J27" t="str">
-        <v>8/3/2025, 2:39:16 AM</v>
-      </c>
-      <c r="K27" t="str">
-        <v>2025-08-03T09:39:16.333Z</v>
-      </c>
-      <c r="L27" t="str">
-        <v>8/3/2025, 5:39:16 AM</v>
-      </c>
-      <c r="M27" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="N27" t="str">
-        <v>BHG 201</v>
-      </c>
-      <c r="O27" t="str">
-        <v>Ben Hill Griffin</v>
-      </c>
-      <c r="P27" t="str">
-        <v>2025-08-03T06:39:16.333Z</v>
-      </c>
-      <c r="Q27" t="str">
-        <v>8/3/2025, 2:39:16 AM</v>
-      </c>
-      <c r="R27" t="str">
-        <v>2025-08-03T08:22:16.333Z</v>
-      </c>
-      <c r="S27" t="str">
-        <v>8/3/2025, 4:22:16 AM</v>
-      </c>
-      <c r="T27">
-        <v>103</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T27"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:T30"/>
   <sheetData>
     <row r="1">
@@ -36361,7 +33063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:T36"/>
   <sheetData>
